--- a/Models/Молоко/results/Молоко - Результаты прогнозов SARIMA.xlsx
+++ b/Models/Молоко/results/Молоко - Результаты прогнозов SARIMA.xlsx
@@ -488,12 +488,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -503,26 +503,26 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(1, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3883.57</v>
+        <v>1406.68</v>
       </c>
       <c r="G2" t="n">
-        <v>3851.82</v>
+        <v>1233.06</v>
       </c>
       <c r="H2" t="n">
-        <v>29.33</v>
+        <v>6.16</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>[7344.14, 8359.17, 12835.03]</t>
+          <t>[22236.04, 21464.76, 16281.72]</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>[10829.7, 11876.6, 17387.5]</t>
+          <t>[22673.0, 22635.3, 18373.4]</t>
         </is>
       </c>
     </row>
@@ -534,12 +534,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -553,22 +553,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2413.25</v>
+        <v>1543.37</v>
       </c>
       <c r="G3" t="n">
-        <v>1991.45</v>
+        <v>1477.56</v>
       </c>
       <c r="H3" t="n">
-        <v>10.73</v>
+        <v>8.24</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>[12157.07, 19465.54, 23836.95]</t>
+          <t>[21786.65, 16542.25, 14197.01]</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>[11876.6, 17387.5, 20221.1]</t>
+          <t>[22635.3, 18373.4, 15949.9]</t>
         </is>
       </c>
     </row>
@@ -580,12 +580,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -599,22 +599,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3371.51</v>
+        <v>1130.81</v>
       </c>
       <c r="G4" t="n">
-        <v>3158.34</v>
+        <v>1075.5</v>
       </c>
       <c r="H4" t="n">
-        <v>14.87</v>
+        <v>6.35</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>[19117.23, 23347.32, 28677.89]</t>
+          <t>[17031.0, 14647.81, 15659.38]</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>[17387.5, 20221.1, 24058.8]</t>
+          <t>[18373.4, 15949.9, 16241.4]</t>
         </is>
       </c>
     </row>
@@ -626,12 +626,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -645,22 +645,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2301.28</v>
+        <v>1882.56</v>
       </c>
       <c r="G5" t="n">
-        <v>2220.63</v>
+        <v>1350.21</v>
       </c>
       <c r="H5" t="n">
-        <v>9.01</v>
+        <v>11.14</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>[21654.74, 26385.66, 31178.4]</t>
+          <t>[15530.89, 16667.58, 8172.65]</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>[20221.1, 24058.8, 28277.0]</t>
+          <t>[15949.9, 16241.4, 11378.1]</t>
         </is>
       </c>
     </row>
@@ -672,12 +672,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -691,22 +691,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>952.33</v>
+        <v>2333.48</v>
       </c>
       <c r="G6" t="n">
-        <v>933.11</v>
+        <v>2121.25</v>
       </c>
       <c r="H6" t="n">
-        <v>3.56</v>
+        <v>17.53</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>[25005.19, 29436.37, 26961.26]</t>
+          <t>[17011.32, 8360.78, 9498.68]</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>[24058.8, 28277.0, 26267.7]</t>
+          <t>[16241.4, 11378.1, 12075.2]</t>
         </is>
       </c>
     </row>
@@ -718,12 +718,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -737,22 +737,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>334.35</v>
+        <v>3466.05</v>
       </c>
       <c r="G7" t="n">
-        <v>306.15</v>
+        <v>3432.92</v>
       </c>
       <c r="H7" t="n">
-        <v>1.23</v>
+        <v>25.24</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>[28584.63, 26126.86, 22203.0]</t>
+          <t>[8075.45, 9151.69, 14041.11]</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>[28277.0, 26267.7, 22673.0]</t>
+          <t>[11378.1, 12075.2, 18113.7]</t>
         </is>
       </c>
     </row>
@@ -764,12 +764,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -779,26 +779,26 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>(1, 1, 1, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>922.3</v>
+        <v>1394.71</v>
       </c>
       <c r="G8" t="n">
-        <v>809.99</v>
+        <v>1113.51</v>
       </c>
       <c r="H8" t="n">
-        <v>3.5</v>
+        <v>5.8</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>[25911.45, 22006.83, 21227.74]</t>
+          <t>[12212.39, 19129.63, 22723.5]</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>[26267.7, 22673.0, 22635.3]</t>
+          <t>[12075.2, 18113.7, 20536.1]</t>
         </is>
       </c>
     </row>
@@ -810,12 +810,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -825,26 +825,26 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>(1, 1, 1, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1406.68</v>
+        <v>1950.39</v>
       </c>
       <c r="G9" t="n">
-        <v>1233.06</v>
+        <v>1812.72</v>
       </c>
       <c r="H9" t="n">
-        <v>6.16</v>
+        <v>8.27</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>[22236.04, 21464.76, 16281.72]</t>
+          <t>[18973.16, 22516.37, 27504.14]</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>[22673.0, 22635.3, 18373.4]</t>
+          <t>[18113.7, 20536.1, 24905.7]</t>
         </is>
       </c>
     </row>
@@ -856,12 +856,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -871,26 +871,26 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>(1, 1, 1, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1543.37</v>
+        <v>1769.21</v>
       </c>
       <c r="G10" t="n">
-        <v>1477.56</v>
+        <v>1693.01</v>
       </c>
       <c r="H10" t="n">
-        <v>8.24</v>
+        <v>6.73</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>[21786.65, 16542.25, 14197.01]</t>
+          <t>[21716.06, 26409.87, 30886.49]</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>[22635.3, 18373.4, 15949.9]</t>
+          <t>[20536.1, 24905.7, 28491.6]</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -917,26 +917,26 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>(1, 1, 1, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1130.81</v>
+        <v>1245.29</v>
       </c>
       <c r="G11" t="n">
-        <v>1075.5</v>
+        <v>1086.57</v>
       </c>
       <c r="H11" t="n">
-        <v>6.35</v>
+        <v>4.15</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>[17031.0, 14647.81, 15659.38]</t>
+          <t>[25293.06, 29493.65, 27250.21]</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>[18373.4, 15949.9, 16241.4]</t>
+          <t>[24905.7, 28491.6, 25379.9]</t>
         </is>
       </c>
     </row>
@@ -948,12 +948,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -967,22 +967,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1046.62</v>
+        <v>1216.03</v>
       </c>
       <c r="G12" t="n">
-        <v>1039.53</v>
+        <v>1212.47</v>
       </c>
       <c r="H12" t="n">
-        <v>15.68</v>
+        <v>6.99</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>[2657.86, 6577.73, 13073.51]</t>
+          <t>[18366.56, 16959.54, 13456.69]</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>[3531.8, 7660.0, 14235.9]</t>
+          <t>[19708.6, 18126.4, 14585.2]</t>
         </is>
       </c>
     </row>
@@ -994,12 +994,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1013,22 +1013,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1548.61</v>
+        <v>801.58</v>
       </c>
       <c r="G13" t="n">
-        <v>1449.43</v>
+        <v>776.45</v>
       </c>
       <c r="H13" t="n">
-        <v>12.22</v>
+        <v>5.51</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>[8344.88, 16154.75, 13991.77]</t>
+          <t>[17480.02, 13960.05, 11121.68]</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>[7660.0, 14235.9, 12247.2]</t>
+          <t>[18126.4, 14585.2, 12179.5]</t>
         </is>
       </c>
     </row>
@@ -1040,12 +1040,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1055,26 +1055,26 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(1, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1738.94</v>
+        <v>573.16</v>
       </c>
       <c r="G14" t="n">
-        <v>1665.41</v>
+        <v>518.74</v>
       </c>
       <c r="H14" t="n">
-        <v>11.88</v>
+        <v>4.19</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>[15633.76, 13479.08, 17391.38]</t>
+          <t>[14205.45, 11318.05, 10558.78]</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>[14235.9, 12247.2, 15024.9]</t>
+          <t>[14585.2, 12179.5, 10873.8]</t>
         </is>
       </c>
     </row>
@@ -1086,12 +1086,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1101,26 +1101,26 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(1, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1251.69</v>
+        <v>838.54</v>
       </c>
       <c r="G15" t="n">
-        <v>1180.59</v>
+        <v>715.71</v>
       </c>
       <c r="H15" t="n">
-        <v>6.75</v>
+        <v>13.95</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>[12839.85, 16487.7, 27710.44]</t>
+          <t>[11462.53, 10693.85, 2394.88]</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>[12247.2, 15024.9, 26224.1]</t>
+          <t>[12179.5, 10873.8, 3645.1]</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1147,26 +1147,26 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(1, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>934.9</v>
+        <v>1411.23</v>
       </c>
       <c r="G16" t="n">
-        <v>928.28</v>
+        <v>1153.31</v>
       </c>
       <c r="H16" t="n">
-        <v>4.76</v>
+        <v>20.43</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>[16108.61, 27094.17, 21280.13]</t>
+          <t>[11011.29, 2451.06, 5674.51]</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>[15024.9, 26224.1, 22111.2]</t>
+          <t>[10873.8, 3645.1, 7802.9]</t>
         </is>
       </c>
     </row>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1193,26 +1193,26 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(1, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1409.2</v>
+        <v>2651.07</v>
       </c>
       <c r="G17" t="n">
-        <v>1146.41</v>
+        <v>2412.36</v>
       </c>
       <c r="H17" t="n">
-        <v>5.54</v>
+        <v>29.13</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>[26240.27, 20621.73, 17775.01]</t>
+          <t>[2436.2, 5641.3, 10717.61]</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>[26224.1, 22111.2, 19708.6]</t>
+          <t>[3645.1, 7802.9, 14584.2]</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1243,22 +1243,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1733.02</v>
+        <v>667.3200000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>1723.46</v>
+        <v>544.88</v>
       </c>
       <c r="H18" t="n">
-        <v>8.720000000000001</v>
+        <v>4.03</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>[20610.09, 17762.09, 16403.64]</t>
+          <t>[7806.04, 15450.08, 13316.63]</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>[22111.2, 19708.6, 18126.4]</t>
+          <t>[7802.9, 14584.2, 12551.0]</t>
         </is>
       </c>
     </row>
@@ -1270,17 +1270,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1289,22 +1289,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1216.03</v>
+        <v>1801.47</v>
       </c>
       <c r="G19" t="n">
-        <v>1212.47</v>
+        <v>1723.41</v>
       </c>
       <c r="H19" t="n">
-        <v>6.99</v>
+        <v>12.02</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>[18366.56, 16959.54, 13456.69]</t>
+          <t>[15926.55, 13913.73, 17861.35]</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>[19708.6, 18126.4, 14585.2]</t>
+          <t>[14584.2, 12551.0, 15396.2]</t>
         </is>
       </c>
     </row>
@@ -1316,41 +1316,41 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>(1, 1, 1, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>801.58</v>
+        <v>1852.58</v>
       </c>
       <c r="G20" t="n">
-        <v>776.45</v>
+        <v>1686.37</v>
       </c>
       <c r="H20" t="n">
-        <v>5.51</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>[17480.02, 13960.05, 11121.68]</t>
+          <t>[13310.83, 17057.52, 29476.07]</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>[18126.4, 14585.2, 12179.5]</t>
+          <t>[12551.0, 15396.2, 26838.1]</t>
         </is>
       </c>
     </row>
@@ -1362,41 +1362,41 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>(1, 1, 1, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>573.16</v>
+        <v>1349.89</v>
       </c>
       <c r="G21" t="n">
-        <v>518.74</v>
+        <v>1279.54</v>
       </c>
       <c r="H21" t="n">
-        <v>4.19</v>
+        <v>6.05</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>[14205.45, 11318.05, 10558.78]</t>
+          <t>[16576.2, 28687.04, 23314.78]</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>[14585.2, 12179.5, 10873.8]</t>
+          <t>[15396.2, 26838.1, 22505.1]</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1423,26 +1423,26 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>6401.64</v>
+        <v>1203.35</v>
       </c>
       <c r="G22" t="n">
-        <v>6363.01</v>
+        <v>1115.77</v>
       </c>
       <c r="H22" t="n">
-        <v>36.46</v>
+        <v>3.56</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>[11229.68, 9768.26, 12239.62]</t>
+          <t>[31936.92, 33256.72, 28357.99]</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>[18455.6, 15274.2, 18596.8]</t>
+          <t>[32883.5, 32588.5, 30090.5]</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1473,22 +1473,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1666.08</v>
+        <v>1348.73</v>
       </c>
       <c r="G23" t="n">
-        <v>1562.48</v>
+        <v>1312.53</v>
       </c>
       <c r="H23" t="n">
-        <v>8.6</v>
+        <v>4.79</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>[16105.89, 20206.57, 21432.89]</t>
+          <t>[34222.42, 29197.6, 23441.57]</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>[15274.2, 18596.8, 19186.9]</t>
+          <t>[32588.5, 30090.5, 22030.8]</t>
         </is>
       </c>
     </row>
@@ -1500,12 +1500,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1515,26 +1515,26 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>(0, 1, 2, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1454.16</v>
+        <v>2948.43</v>
       </c>
       <c r="G24" t="n">
-        <v>1373.6</v>
+        <v>2370.2</v>
       </c>
       <c r="H24" t="n">
-        <v>6.71</v>
+        <v>12.68</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>[19373.48, 20586.03, 24406.28]</t>
+          <t>[27855.08, 22323.75, 11069.77]</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>[18596.8, 19186.9, 22461.3]</t>
+          <t>[30090.5, 22030.8, 15652.0]</t>
         </is>
       </c>
     </row>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1561,26 +1561,26 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>(0, 1, 2, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>7620.33</v>
+        <v>2522.14</v>
       </c>
       <c r="G25" t="n">
-        <v>4896.83</v>
+        <v>2225.67</v>
       </c>
       <c r="H25" t="n">
-        <v>15.87</v>
+        <v>12.67</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>[19765.3, 23422.34, 19457.46]</t>
+          <t>[24057.92, 11884.21, 17686.8]</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>[19186.9, 22461.3, 32608.5]</t>
+          <t>[22030.8, 15652.0, 18568.9]</t>
         </is>
       </c>
     </row>
@@ -1592,12 +1592,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1607,26 +1607,26 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>(0, 1, 2, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>10804.05</v>
+        <v>3445.69</v>
       </c>
       <c r="G26" t="n">
-        <v>8899.41</v>
+        <v>3266.54</v>
       </c>
       <c r="H26" t="n">
-        <v>28.66</v>
+        <v>19.83</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>[22727.78, 18762.97, 17138.09]</t>
+          <t>[10843.94, 16219.96, 13753.78]</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>[22461.3, 32608.5, 29724.3]</t>
+          <t>[15652.0, 18568.9, 16396.4]</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1653,26 +1653,26 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>(0, 1, 2, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>13997.23</v>
+        <v>3584</v>
       </c>
       <c r="G27" t="n">
-        <v>13976.97</v>
+        <v>3549.73</v>
       </c>
       <c r="H27" t="n">
-        <v>44.02</v>
+        <v>19.28</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>[18348.44, 16777.73, 18159.23]</t>
+          <t>[22636.07, 19280.17, 23848.76]</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>[32608.5, 29724.3, 32883.5]</t>
+          <t>[18568.9, 16396.4, 20150.5]</t>
         </is>
       </c>
     </row>
@@ -1684,17 +1684,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>(0, 1, 0)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1703,22 +1703,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1457.24</v>
+        <v>832.65</v>
       </c>
       <c r="G28" t="n">
-        <v>1305.13</v>
+        <v>548.48</v>
       </c>
       <c r="H28" t="n">
-        <v>4.1</v>
+        <v>2.83</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>[28585.19, 30714.59, 31981.12]</t>
+          <t>[16220.36, 20189.0, 21247.39]</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>[29724.3, 32883.5, 32588.5]</t>
+          <t>[16396.4, 20150.5, 19816.5]</t>
         </is>
       </c>
     </row>
@@ -1730,17 +1730,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>(0, 1, 0)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1749,22 +1749,22 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1203.35</v>
+        <v>1632.97</v>
       </c>
       <c r="G29" t="n">
-        <v>1115.77</v>
+        <v>1384.09</v>
       </c>
       <c r="H29" t="n">
-        <v>3.56</v>
+        <v>6.41</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>[31936.92, 33256.72, 28357.99]</t>
+          <t>[20372.97, 21443.25, 25516.04]</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>[32883.5, 32588.5, 30090.5]</t>
+          <t>[20150.5, 19816.5, 23213.0]</t>
         </is>
       </c>
     </row>
@@ -1776,17 +1776,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>(0, 1, 0)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1795,22 +1795,22 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1348.73</v>
+        <v>1808.31</v>
       </c>
       <c r="G30" t="n">
-        <v>1312.53</v>
+        <v>1788.63</v>
       </c>
       <c r="H30" t="n">
-        <v>4.79</v>
+        <v>7.25</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>[34222.42, 29197.6, 23441.57]</t>
+          <t>[21249.99, 25286.76, 31401.85]</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>[32588.5, 30090.5, 22030.8]</t>
+          <t>[19816.5, 23213.0, 33260.5]</t>
         </is>
       </c>
     </row>
@@ -1822,17 +1822,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>(0, 1, 0)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1841,22 +1841,22 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2948.43</v>
+        <v>3607.49</v>
       </c>
       <c r="G31" t="n">
-        <v>2370.2</v>
+        <v>3103.16</v>
       </c>
       <c r="H31" t="n">
-        <v>12.68</v>
+        <v>9.9</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>[27855.08, 22323.75, 11069.77]</t>
+          <t>[23857.36, 29664.36, 26369.91]</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>[30090.5, 22030.8, 15652.0]</t>
+          <t>[23213.0, 33260.5, 31438.9]</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1883,26 +1883,26 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>819.7</v>
+        <v>115.28</v>
       </c>
       <c r="G32" t="n">
-        <v>795.37</v>
+        <v>97.03</v>
       </c>
       <c r="H32" t="n">
-        <v>59.24</v>
+        <v>3.27</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>[440.72, 497.97, 684.1]</t>
+          <t>[3086.84, 3183.24, 1475.42]</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>[1105.5, 1143.8, 1759.6]</t>
+          <t>[3263.7, 3272.5, 1500.4]</t>
         </is>
       </c>
     </row>
@@ -1914,17 +1914,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>(0, 1, 0)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1933,22 +1933,22 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>206.45</v>
+        <v>51.67</v>
       </c>
       <c r="G33" t="n">
-        <v>174.65</v>
+        <v>50.69</v>
       </c>
       <c r="H33" t="n">
-        <v>8.93</v>
+        <v>2.29</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>[1260.18, 1838.35, 3034.91]</t>
+          <t>[3337.17, 1546.02, 2220.91]</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>[1143.8, 1759.6, 2706.1]</t>
+          <t>[3272.5, 1500.4, 2262.7]</t>
         </is>
       </c>
     </row>
@@ -1960,12 +1960,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1979,22 +1979,22 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>101.29</v>
+        <v>139.16</v>
       </c>
       <c r="G34" t="n">
-        <v>96.22</v>
+        <v>108.52</v>
       </c>
       <c r="H34" t="n">
-        <v>3.27</v>
+        <v>4.41</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>[1680.76, 2775.32, 5209.61]</t>
+          <t>[1520.9, 2184.81, 2475.12]</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>[1759.6, 2706.1, 5069.0]</t>
+          <t>[1500.4, 2262.7, 2702.3]</t>
         </is>
       </c>
     </row>
@@ -2006,12 +2006,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2025,22 +2025,22 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>226.59</v>
+        <v>310.81</v>
       </c>
       <c r="G35" t="n">
-        <v>182.43</v>
+        <v>273.61</v>
       </c>
       <c r="H35" t="n">
-        <v>4.68</v>
+        <v>18.65</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>[2885.88, 5417.35, 3720.42]</t>
+          <t>[2159.89, 2446.88, 640.0]</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>[2706.1, 5069.0, 3739.6]</t>
+          <t>[2262.7, 2702.3, 1102.6]</t>
         </is>
       </c>
     </row>
@@ -2052,12 +2052,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2071,22 +2071,22 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>151.68</v>
+        <v>360.94</v>
       </c>
       <c r="G36" t="n">
-        <v>137.84</v>
+        <v>337.63</v>
       </c>
       <c r="H36" t="n">
-        <v>3.95</v>
+        <v>27.31</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>[5130.23, 3523.36, 2668.64]</t>
+          <t>[2544.78, 664.77, 729.86]</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>[5069.0, 3739.6, 2804.7]</t>
+          <t>[2702.3, 1102.6, 1147.4]</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2117,22 +2117,22 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>268.74</v>
+        <v>511.35</v>
       </c>
       <c r="G37" t="n">
-        <v>256.93</v>
+        <v>491.17</v>
       </c>
       <c r="H37" t="n">
-        <v>7.82</v>
+        <v>36.09</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>[3487.51, 2641.74, 2907.96]</t>
+          <t>[699.91, 768.39, 1095.38]</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>[3739.6, 2804.7, 3263.7]</t>
+          <t>[1102.6, 1147.4, 1787.2]</t>
         </is>
       </c>
     </row>
@@ -2144,41 +2144,41 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(0, 1, 0)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>115.78</v>
+        <v>44.88</v>
       </c>
       <c r="G38" t="n">
-        <v>90.76000000000001</v>
+        <v>42.71</v>
       </c>
       <c r="H38" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>[2802.15, 3085.07, 3181.41]</t>
+          <t>[1208.81, 1758.61, 2801.77]</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>[2804.7, 3263.7, 3272.5]</t>
+          <t>[1147.4, 1787.2, 2839.9]</t>
         </is>
       </c>
     </row>
@@ -2190,12 +2190,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2205,26 +2205,26 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>115.28</v>
+        <v>277.48</v>
       </c>
       <c r="G39" t="n">
-        <v>97.03</v>
+        <v>238.66</v>
       </c>
       <c r="H39" t="n">
-        <v>3.27</v>
+        <v>6.73</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>[3086.84, 3183.24, 1475.42]</t>
+          <t>[1675.63, 2671.65, 4996.55]</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>[3263.7, 3272.5, 1500.4]</t>
+          <t>[1787.2, 2839.9, 5432.7]</t>
         </is>
       </c>
     </row>
@@ -2236,41 +2236,41 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(1, 1, 0)</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>51.67</v>
+        <v>167.58</v>
       </c>
       <c r="G40" t="n">
-        <v>50.69</v>
+        <v>137.78</v>
       </c>
       <c r="H40" t="n">
-        <v>2.29</v>
+        <v>3.16</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>[3337.17, 1546.02, 2220.91]</t>
+          <t>[2822.88, 5286.6, 3781.97]</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>[3272.5, 1500.4, 2262.7]</t>
+          <t>[2839.9, 5432.7, 4032.2]</t>
         </is>
       </c>
     </row>
@@ -2282,41 +2282,41 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(1, 1, 0)</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>139.16</v>
+        <v>177.1</v>
       </c>
       <c r="G41" t="n">
-        <v>108.52</v>
+        <v>171.05</v>
       </c>
       <c r="H41" t="n">
-        <v>4.41</v>
+        <v>4.46</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>[1520.9, 2184.81, 2475.12]</t>
+          <t>[5313.99, 3801.77, 2823.29]</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>[1500.4, 2262.7, 2702.3]</t>
+          <t>[5432.7, 4032.2, 2987.3]</t>
         </is>
       </c>
     </row>
@@ -2328,41 +2328,41 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>(2, 1, 2)</t>
+          <t>(0, 1, 0)</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1309.04</v>
+        <v>1568.93</v>
       </c>
       <c r="G42" t="n">
-        <v>1081.77</v>
+        <v>1210.7</v>
       </c>
       <c r="H42" t="n">
-        <v>9.529999999999999</v>
+        <v>5.9</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>[8858.65, 10444.37, 14526.15]</t>
+          <t>[24580.44, 21137.56, 16523.7]</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>[10951.0, 11242.4, 14881.1]</t>
+          <t>[25528.8, 21278.6, 19066.4]</t>
         </is>
       </c>
     </row>
@@ -2374,41 +2374,41 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>(0, 1, 0)</t>
+          <t>(2, 1, 2)</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>(2, 1, 0, 12)</t>
+          <t>(1, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>3811.02</v>
+        <v>2861.12</v>
       </c>
       <c r="G43" t="n">
-        <v>3541.37</v>
+        <v>2520.73</v>
       </c>
       <c r="H43" t="n">
-        <v>22.95</v>
+        <v>12.91</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>[12890.84, 18833.71, 23200.37]</t>
+          <t>[22293.06, 16815.41, 15097.07]</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>[11242.4, 14881.1, 18177.3]</t>
+          <t>[21278.6, 19066.4, 19393.8]</t>
         </is>
       </c>
     </row>
@@ -2420,12 +2420,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2435,26 +2435,26 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>(2, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2464.37</v>
+        <v>7041.1</v>
       </c>
       <c r="G44" t="n">
-        <v>2325.95</v>
+        <v>5929.97</v>
       </c>
       <c r="H44" t="n">
-        <v>12.88</v>
+        <v>26.07</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>[16402.8, 20191.63, 23293.73]</t>
+          <t>[16629.21, 15248.6, 14227.46]</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>[14881.1, 18177.3, 19851.9]</t>
+          <t>[19066.4, 19393.8, 25435.0]</t>
         </is>
       </c>
     </row>
@@ -2466,12 +2466,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2481,26 +2481,26 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>(2, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>4752.02</v>
+        <v>5583.49</v>
       </c>
       <c r="G45" t="n">
-        <v>3179.59</v>
+        <v>4591.06</v>
       </c>
       <c r="H45" t="n">
-        <v>12.59</v>
+        <v>23.06</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>[18312.08, 21125.38, 18415.49]</t>
+          <t>[17528.16, 16386.82, 9066.55]</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>[18177.3, 19851.9, 26546.0]</t>
+          <t>[19393.8, 25435.0, 11925.9]</t>
         </is>
       </c>
     </row>
@@ -2512,12 +2512,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2527,26 +2527,26 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>(2, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>7082.87</v>
+        <v>4493.95</v>
       </c>
       <c r="G46" t="n">
-        <v>6126.83</v>
+        <v>3727.6</v>
       </c>
       <c r="H46" t="n">
-        <v>23.5</v>
+        <v>19.88</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>[20969.75, 18269.85, 17681.03]</t>
+          <t>[18157.68, 9995.66, 11333.75]</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>[19851.9, 26546.0, 26667.5]</t>
+          <t>[25435.0, 11925.9, 13309.0]</t>
         </is>
       </c>
     </row>
@@ -2558,41 +2558,41 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>(0, 1, 0)</t>
+          <t>(2, 1, 2)</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>(2, 1, 0, 12)</t>
+          <t>(1, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>9788.01</v>
+        <v>4689.31</v>
       </c>
       <c r="G47" t="n">
-        <v>9781.030000000001</v>
+        <v>4391.54</v>
       </c>
       <c r="H47" t="n">
-        <v>37.3</v>
+        <v>29.62</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>[17277.08, 16720.3, 15401.82]</t>
+          <t>[14440.3, 17450.31, 24300.43]</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>[26546.0, 26667.5, 25528.8]</t>
+          <t>[11925.9, 13309.0, 17781.5]</t>
         </is>
       </c>
     </row>
@@ -2604,12 +2604,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2623,22 +2623,22 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1461.21</v>
+        <v>889.89</v>
       </c>
       <c r="G48" t="n">
-        <v>1396.98</v>
+        <v>735.2</v>
       </c>
       <c r="H48" t="n">
-        <v>5.68</v>
+        <v>3.76</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>[25524.67, 23528.39, 20230.9]</t>
+          <t>[13337.4, 18821.02, 22956.37]</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>[26667.5, 25528.8, 21278.6]</t>
+          <t>[13309.0, 17781.5, 21818.7]</t>
         </is>
       </c>
     </row>
@@ -2650,12 +2650,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2669,22 +2669,22 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1568.93</v>
+        <v>1531.32</v>
       </c>
       <c r="G49" t="n">
-        <v>1210.7</v>
+        <v>1431.56</v>
       </c>
       <c r="H49" t="n">
-        <v>5.9</v>
+        <v>6.58</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>[24580.44, 21137.56, 16523.7]</t>
+          <t>[18784.2, 22912.07, 26378.62]</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>[25528.8, 21278.6, 19066.4]</t>
+          <t>[17781.5, 21818.7, 24180.0]</t>
         </is>
       </c>
     </row>
@@ -2696,41 +2696,41 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>(2, 1, 2)</t>
+          <t>(0, 1, 0)</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>(1, 1, 1, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>2861.12</v>
+        <v>470.11</v>
       </c>
       <c r="G50" t="n">
-        <v>2520.73</v>
+        <v>374.04</v>
       </c>
       <c r="H50" t="n">
-        <v>12.91</v>
+        <v>1.51</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>[22293.06, 16815.41, 15097.07]</t>
+          <t>[21686.87, 24953.8, 29938.9]</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>[21278.6, 19066.4, 19393.8]</t>
+          <t>[21818.7, 24180.0, 30155.4]</t>
         </is>
       </c>
     </row>
@@ -2742,12 +2742,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2761,22 +2761,22 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>7041.1</v>
+        <v>859.71</v>
       </c>
       <c r="G51" t="n">
-        <v>5929.97</v>
+        <v>707.42</v>
       </c>
       <c r="H51" t="n">
-        <v>26.07</v>
+        <v>2.69</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>[16629.21, 15248.6, 14227.46]</t>
+          <t>[25109.96, 30125.69, 29409.29]</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>[19066.4, 19393.8, 25435.0]</t>
+          <t>[24180.0, 30155.4, 28246.7]</t>
         </is>
       </c>
     </row>
@@ -2788,17 +2788,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(0, 0, 3)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2807,22 +2807,22 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>33.61</v>
+        <v>53.79</v>
       </c>
       <c r="G52" t="n">
-        <v>31.63</v>
+        <v>34.56</v>
       </c>
       <c r="H52" t="n">
-        <v>87.03</v>
+        <v>122.04</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>[8.8, 8.37, 0.53]</t>
+          <t>[21.15, 27.38, 121.54]</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>[48.2, 48.3, 16.1]</t>
+          <t>[27.5, 22.9, 28.7]</t>
         </is>
       </c>
     </row>
@@ -2834,17 +2834,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(0, 0, 3)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2853,22 +2853,22 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>23.54</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="G53" t="n">
-        <v>21.57</v>
+        <v>61.13</v>
       </c>
       <c r="H53" t="n">
-        <v>72.43000000000001</v>
+        <v>216.73</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>[13.4, 1.07, 13.83]</t>
+          <t>[31.08, 139.96, 92.16]</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>[48.3, 16.1, 28.6]</t>
+          <t>[22.9, 28.7, 28.2]</t>
         </is>
       </c>
     </row>
@@ -2880,17 +2880,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(2, 0, 0)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2899,22 +2899,22 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>8.720000000000001</v>
+        <v>58.8</v>
       </c>
       <c r="G54" t="n">
-        <v>7.21</v>
+        <v>53.88</v>
       </c>
       <c r="H54" t="n">
-        <v>37.92</v>
+        <v>181.21</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>[1.96, 24.96, 32.94]</t>
+          <t>[111.9, 81.08, 64.16]</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>[16.1, 28.6, 29.1]</t>
+          <t>[28.7, 28.2, 38.6]</t>
         </is>
       </c>
     </row>
@@ -2926,17 +2926,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(2, 0, 0)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2945,22 +2945,22 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>51.19</v>
+        <v>12.08</v>
       </c>
       <c r="G55" t="n">
-        <v>45.74</v>
+        <v>10.05</v>
       </c>
       <c r="H55" t="n">
-        <v>163.22</v>
+        <v>35.7</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>[47.5, 72.38, 102.34]</t>
+          <t>[47.47, 35.1, 17.51]</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>[28.6, 29.1, 27.3]</t>
+          <t>[28.2, 38.6, 24.9]</t>
         </is>
       </c>
     </row>
@@ -2972,12 +2972,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2991,22 +2991,22 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>31.04</v>
+        <v>11.2</v>
       </c>
       <c r="G56" t="n">
-        <v>30.33</v>
+        <v>11.18</v>
       </c>
       <c r="H56" t="n">
-        <v>107.8</v>
+        <v>39.47</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>[58.72, 66.03, 51.04]</t>
+          <t>[28.27, 13.8, 13.61]</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>[29.1, 27.3, 28.4]</t>
+          <t>[38.6, 24.9, 25.7]</t>
         </is>
       </c>
     </row>
@@ -3018,12 +3018,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3037,22 +3037,22 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>14.81</v>
+        <v>14.01</v>
       </c>
       <c r="G57" t="n">
-        <v>12.12</v>
+        <v>13.07</v>
       </c>
       <c r="H57" t="n">
-        <v>43.93</v>
+        <v>51.88</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>[51.02, 37.47, 23.94]</t>
+          <t>[15.77, 15.78, 4.93]</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>[27.3, 28.4, 27.5]</t>
+          <t>[24.9, 25.7, 25.1]</t>
         </is>
       </c>
     </row>
@@ -3064,17 +3064,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>(0, 0, 3)</t>
+          <t>(2, 0, 0)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3083,22 +3083,22 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>5.42</v>
+        <v>13.01</v>
       </c>
       <c r="G58" t="n">
-        <v>4.77</v>
+        <v>11.9</v>
       </c>
       <c r="H58" t="n">
-        <v>17.62</v>
+        <v>45.94</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>[23.97, 19.41, 24.7]</t>
+          <t>[19.0, 6.03, 17.86]</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>[28.4, 27.5, 22.9]</t>
+          <t>[25.7, 25.1, 27.8]</t>
         </is>
       </c>
     </row>
@@ -3110,17 +3110,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>(0, 0, 3)</t>
+          <t>(2, 0, 0)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3129,22 +3129,22 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>53.79</v>
+        <v>11.63</v>
       </c>
       <c r="G59" t="n">
-        <v>34.56</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="H59" t="n">
-        <v>122.04</v>
+        <v>37.26</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>[21.15, 27.38, 121.54]</t>
+          <t>[6.74, 20.25, 26.38]</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>[27.5, 22.9, 28.7]</t>
+          <t>[25.1, 27.8, 29.8]</t>
         </is>
       </c>
     </row>
@@ -3156,41 +3156,41 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>(0, 0, 3)</t>
+          <t>(2, 0, 0)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(2, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>74.23999999999999</v>
+        <v>13.09</v>
       </c>
       <c r="G60" t="n">
-        <v>61.13</v>
+        <v>10.65</v>
       </c>
       <c r="H60" t="n">
-        <v>216.73</v>
+        <v>37.13</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>[31.08, 139.96, 92.16]</t>
+          <t>[28.01, 43.35, 46.08]</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>[22.9, 28.7, 28.2]</t>
+          <t>[27.8, 29.8, 27.9]</t>
         </is>
       </c>
     </row>
@@ -3202,12 +3202,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3217,26 +3217,26 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(2, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>58.8</v>
+        <v>13.77</v>
       </c>
       <c r="G61" t="n">
-        <v>53.88</v>
+        <v>13.11</v>
       </c>
       <c r="H61" t="n">
-        <v>181.21</v>
+        <v>46.23</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>[111.9, 81.08, 64.16]</t>
+          <t>[43.25, 46.0, 34.88]</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>[28.7, 28.2, 38.6]</t>
+          <t>[29.8, 27.9, 27.1]</t>
         </is>
       </c>
     </row>
@@ -3248,12 +3248,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3267,22 +3267,22 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>0.77</v>
+        <v>1.79</v>
       </c>
       <c r="G62" t="n">
-        <v>0.76</v>
+        <v>1.6</v>
       </c>
       <c r="H62" t="n">
-        <v>7.11</v>
+        <v>9.76</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>[10.62, 10.5, 10.4]</t>
+          <t>[24.19, 14.72, 11.09]</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>[11.2, 9.7, 11.3]</t>
+          <t>[25.0, 17.4, 12.4]</t>
         </is>
       </c>
     </row>
@@ -3294,12 +3294,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3313,22 +3313,22 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>2.87</v>
+        <v>1.77</v>
       </c>
       <c r="G63" t="n">
-        <v>2.18</v>
+        <v>1.62</v>
       </c>
       <c r="H63" t="n">
-        <v>13.17</v>
+        <v>13.46</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>[10.6, 10.49, 16.09]</t>
+          <t>[14.8, 11.14, 5.59]</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>[9.7, 11.3, 20.9]</t>
+          <t>[17.4, 12.4, 6.6]</t>
         </is>
       </c>
     </row>
@@ -3340,12 +3340,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3359,22 +3359,22 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>3.63</v>
+        <v>0.75</v>
       </c>
       <c r="G64" t="n">
-        <v>3.22</v>
+        <v>0.64</v>
       </c>
       <c r="H64" t="n">
-        <v>17.03</v>
+        <v>18.1</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>[10.33, 15.88, 16.24]</t>
+          <t>[11.44, 5.72, 0.27]</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>[11.3, 20.9, 19.9]</t>
+          <t>[12.4, 6.6, 0.2]</t>
         </is>
       </c>
     </row>
@@ -3386,12 +3386,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3405,22 +3405,22 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>3.47</v>
+        <v>2.01</v>
       </c>
       <c r="G65" t="n">
-        <v>3.13</v>
+        <v>1.42</v>
       </c>
       <c r="H65" t="n">
-        <v>15.55</v>
+        <v>32.76</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>[16.13, 16.45, 19.16]</t>
+          <t>[5.8, 0.27, 9.99]</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>[20.9, 19.9, 18.0]</t>
+          <t>[6.6, 0.2, 6.6]</t>
         </is>
       </c>
     </row>
@@ -3432,12 +3432,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3451,22 +3451,22 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="G66" t="n">
-        <v>2.43</v>
+        <v>2.03</v>
       </c>
       <c r="H66" t="n">
-        <v>11.61</v>
+        <v>43.49</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>[17.18, 19.88, 27.8]</t>
+          <t>[0.28, 10.17, 8.74]</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>[19.9, 18.0, 25.1]</t>
+          <t>[0.2, 6.6, 6.3]</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3497,22 +3497,22 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>2.35</v>
+        <v>2.72</v>
       </c>
       <c r="G67" t="n">
-        <v>1.91</v>
+        <v>2.69</v>
       </c>
       <c r="H67" t="n">
-        <v>8.85</v>
+        <v>40.76</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>[20.38, 28.39, 25.05]</t>
+          <t>[9.66, 8.36, 9.74]</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>[18.0, 25.1, 25.0]</t>
+          <t>[6.6, 6.3, 6.8]</t>
         </is>
       </c>
     </row>
@@ -3524,12 +3524,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3543,22 +3543,22 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>2.12</v>
+        <v>3.56</v>
       </c>
       <c r="G68" t="n">
-        <v>1.85</v>
+        <v>3.14</v>
       </c>
       <c r="H68" t="n">
-        <v>8.83</v>
+        <v>35.49</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>[27.8, 24.61, 14.93]</t>
+          <t>[7.84, 9.24, 17.25]</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>[25.1, 25.0, 17.4]</t>
+          <t>[6.3, 6.8, 11.8]</t>
         </is>
       </c>
     </row>
@@ -3570,12 +3570,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3589,22 +3589,22 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1.79</v>
+        <v>4.35</v>
       </c>
       <c r="G69" t="n">
-        <v>1.6</v>
+        <v>4.11</v>
       </c>
       <c r="H69" t="n">
-        <v>9.76</v>
+        <v>40.53</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>[24.19, 14.72, 11.09]</t>
+          <t>[8.88, 16.71, 16.13]</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>[25.0, 17.4, 12.4]</t>
+          <t>[6.8, 11.8, 10.8]</t>
         </is>
       </c>
     </row>
@@ -3616,12 +3616,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3635,22 +3635,22 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>1.77</v>
+        <v>4.22</v>
       </c>
       <c r="G70" t="n">
-        <v>1.62</v>
+        <v>4.21</v>
       </c>
       <c r="H70" t="n">
-        <v>13.46</v>
+        <v>33.13</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>[14.8, 11.14, 5.59]</t>
+          <t>[15.9, 15.51, 14.29]</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>[17.4, 12.4, 6.6]</t>
+          <t>[11.8, 10.8, 18.1]</t>
         </is>
       </c>
     </row>
@@ -3662,12 +3662,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3681,22 +3681,22 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>0.75</v>
+        <v>3.57</v>
       </c>
       <c r="G71" t="n">
-        <v>0.64</v>
+        <v>3.41</v>
       </c>
       <c r="H71" t="n">
-        <v>18.1</v>
+        <v>23.03</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>[11.44, 5.72, 0.27]</t>
+          <t>[14.62, 13.63, 19.47]</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>[12.4, 6.6, 0.2]</t>
+          <t>[10.8, 18.1, 21.4]</t>
         </is>
       </c>
     </row>
@@ -3708,41 +3708,41 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>(1, 1, 2)</t>
+          <t>(1, 1, 1)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>(2, 1, 0, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>608.29</v>
+        <v>627.3200000000001</v>
       </c>
       <c r="G72" t="n">
-        <v>572.35</v>
+        <v>578.88</v>
       </c>
       <c r="H72" t="n">
-        <v>14.76</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>[4239.65, 4275.2, 5239.62]</t>
+          <t>[6059.51, 4704.61, 5383.82]</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>[3430.5, 3968.2, 4638.7]</t>
+          <t>[6371.8, 5602.1, 5910.7]</t>
         </is>
       </c>
     </row>
@@ -3754,12 +3754,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3773,22 +3773,22 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>168.45</v>
+        <v>550.3200000000001</v>
       </c>
       <c r="G73" t="n">
-        <v>149.38</v>
+        <v>523.53</v>
       </c>
       <c r="H73" t="n">
-        <v>3.1</v>
+        <v>9.56</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>[3767.18, 4599.37, 6368.08]</t>
+          <t>[4900.36, 5615.34, 4570.7]</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>[3968.2, 4638.7, 6160.3]</t>
+          <t>[5602.1, 5910.7, 5144.2]</t>
         </is>
       </c>
     </row>
@@ -3800,41 +3800,41 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>(1, 1, 1)</t>
+          <t>(0, 1, 0)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>(1, 1, 1, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>432.43</v>
+        <v>402.07</v>
       </c>
       <c r="G74" t="n">
-        <v>392.38</v>
+        <v>359.35</v>
       </c>
       <c r="H74" t="n">
-        <v>6.21</v>
+        <v>6.47</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>[4809.57, 6550.58, 7781.81]</t>
+          <t>[6337.83, 5256.73, 5917.2]</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>[4638.7, 6160.3, 7165.8]</t>
+          <t>[5910.7, 5144.2, 5378.8]</t>
         </is>
       </c>
     </row>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3865,22 +3865,22 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>448.85</v>
+        <v>327.78</v>
       </c>
       <c r="G75" t="n">
-        <v>393.18</v>
+        <v>285.56</v>
       </c>
       <c r="H75" t="n">
-        <v>5.61</v>
+        <v>6.25</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>[6480.38, 7853.03, 8214.46]</t>
+          <t>[4787.98, 5315.92, 4549.57]</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>[6160.3, 7165.8, 8386.7]</t>
+          <t>[5144.2, 5378.8, 4112.0]</t>
         </is>
       </c>
     </row>
@@ -3892,41 +3892,41 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>(0, 1, 3)</t>
+          <t>(0, 1, 0)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>(1, 1, 1, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>626.2</v>
+        <v>895.4299999999999</v>
       </c>
       <c r="G76" t="n">
-        <v>571.8099999999999</v>
+        <v>842.48</v>
       </c>
       <c r="H76" t="n">
-        <v>7.46</v>
+        <v>18.94</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>[7412.64, 7788.59, 6503.42]</t>
+          <t>[5806.97, 5065.14, 5609.62]</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>[7165.8, 8386.7, 7373.9]</t>
+          <t>[5378.8, 4112.0, 4463.5]</t>
         </is>
       </c>
     </row>
@@ -3938,41 +3938,41 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>(0, 1, 3)</t>
+          <t>(1, 1, 1)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>(1, 1, 1, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>847.34</v>
+        <v>664.42</v>
       </c>
       <c r="G77" t="n">
-        <v>841.11</v>
+        <v>650.96</v>
       </c>
       <c r="H77" t="n">
-        <v>11.51</v>
+        <v>14.05</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>[7597.22, 6389.57, 5622.27]</t>
+          <t>[4608.02, 5099.48, 6004.08]</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>[8386.7, 7373.9, 6371.8]</t>
+          <t>[4112.0, 4463.5, 5183.2]</t>
         </is>
       </c>
     </row>
@@ -3984,17 +3984,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>(0, 1, 3)</t>
+          <t>(1, 1, 1)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4003,22 +4003,22 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>659.17</v>
+        <v>522.86</v>
       </c>
       <c r="G78" t="n">
-        <v>600.3200000000001</v>
+        <v>486.18</v>
       </c>
       <c r="H78" t="n">
-        <v>9.85</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>[6979.95, 5949.78, 4617.11]</t>
+          <t>[4720.03, 5657.92, 7653.5]</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>[7373.9, 6371.8, 5602.1]</t>
+          <t>[4463.5, 5183.2, 6926.2]</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4049,22 +4049,22 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>627.3200000000001</v>
+        <v>490.01</v>
       </c>
       <c r="G79" t="n">
-        <v>578.88</v>
+        <v>420.58</v>
       </c>
       <c r="H79" t="n">
-        <v>9.949999999999999</v>
+        <v>5.96</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>[6059.51, 4704.61, 5383.82]</t>
+          <t>[5357.36, 7247.97, 8521.11]</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>[6371.8, 5602.1, 5910.7]</t>
+          <t>[5183.2, 6926.2, 7755.3]</t>
         </is>
       </c>
     </row>
@@ -4076,12 +4076,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4095,22 +4095,22 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>550.3200000000001</v>
+        <v>657.3</v>
       </c>
       <c r="G80" t="n">
-        <v>523.53</v>
+        <v>561.16</v>
       </c>
       <c r="H80" t="n">
-        <v>9.56</v>
+        <v>7.1</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>[4900.36, 5615.34, 4570.7]</t>
+          <t>[7058.46, 8336.55, 9122.05]</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>[5602.1, 5910.7, 5144.2]</t>
+          <t>[6926.2, 7755.3, 8152.1]</t>
         </is>
       </c>
     </row>
@@ -4122,17 +4122,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>(0, 1, 0)</t>
+          <t>(1, 1, 1)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4141,22 +4141,22 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>402.07</v>
+        <v>768.02</v>
       </c>
       <c r="G81" t="n">
-        <v>359.35</v>
+        <v>740.76</v>
       </c>
       <c r="H81" t="n">
-        <v>6.47</v>
+        <v>9.84</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>[6337.83, 5256.73, 5917.2]</t>
+          <t>[8211.09, 9006.97, 7842.81]</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>[5910.7, 5144.2, 5378.8]</t>
+          <t>[7755.3, 8152.1, 6931.2]</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4183,26 +4183,26 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>4049.1</v>
+        <v>322.89</v>
       </c>
       <c r="G82" t="n">
-        <v>4047.47</v>
+        <v>261.64</v>
       </c>
       <c r="H82" t="n">
-        <v>33.56</v>
+        <v>1.07</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>[7777.56, 7846.78, 8419.76]</t>
+          <t>[25234.37, 24794.42, 15461.63]</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>[11727.3, 11830.5, 12628.7]</t>
+          <t>[24907.0, 24341.0, 15457.5]</t>
         </is>
       </c>
     </row>
@@ -4214,12 +4214,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4233,22 +4233,22 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>1505.55</v>
+        <v>180.04</v>
       </c>
       <c r="G83" t="n">
-        <v>1439.97</v>
+        <v>149.15</v>
       </c>
       <c r="H83" t="n">
-        <v>9.619999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>[10671.83, 11528.07, 17855.59]</t>
+          <t>[24626.91, 15341.69, 14498.14]</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>[11830.5, 12628.7, 19916.2]</t>
+          <t>[24341.0, 15457.5, 14452.4]</t>
         </is>
       </c>
     </row>
@@ -4260,12 +4260,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4275,26 +4275,26 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>(0, 1, 2, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>706.86</v>
+        <v>482.76</v>
       </c>
       <c r="G84" t="n">
-        <v>665.3200000000001</v>
+        <v>355.42</v>
       </c>
       <c r="H84" t="n">
-        <v>3.58</v>
+        <v>2.04</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>[12283.72, 18998.23, 20877.9]</t>
+          <t>[15244.59, 14406.33, 17463.51]</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>[12628.7, 19916.2, 21610.9]</t>
+          <t>[15457.5, 14452.4, 18270.8]</t>
         </is>
       </c>
     </row>
@@ -4306,12 +4306,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4321,26 +4321,26 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>(0, 1, 2, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>477.46</v>
+        <v>1402.6</v>
       </c>
       <c r="G85" t="n">
-        <v>464.05</v>
+        <v>1023.75</v>
       </c>
       <c r="H85" t="n">
-        <v>2.09</v>
+        <v>7.93</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>[19294.77, 21206.47, 28576.2]</t>
+          <t>[14515.48, 17595.39, 9537.75]</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>[19916.2, 21610.9, 28942.5]</t>
+          <t>[14452.4, 18270.8, 11870.5]</t>
         </is>
       </c>
     </row>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4367,26 +4367,26 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>(0, 1, 2, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>158.21</v>
+        <v>1964.98</v>
       </c>
       <c r="G86" t="n">
-        <v>134.46</v>
+        <v>1807.37</v>
       </c>
       <c r="H86" t="n">
-        <v>0.5600000000000001</v>
+        <v>14.48</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>[21580.36, 29080.68, 21973.65]</t>
+          <t>[17553.88, 9515.69, 9599.91]</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>[21610.9, 28942.5, 22208.3]</t>
+          <t>[18270.8, 11870.5, 11950.3]</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4417,22 +4417,22 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>187.78</v>
+        <v>2184.72</v>
       </c>
       <c r="G87" t="n">
-        <v>183.34</v>
+        <v>2183.4</v>
       </c>
       <c r="H87" t="n">
-        <v>0.75</v>
+        <v>17.88</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>[29078.94, 21972.81, 25085.09]</t>
+          <t>[9737.61, 9823.79, 10513.99]</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>[28942.5, 22208.3, 24907.0]</t>
+          <t>[11870.5, 11950.3, 12804.8]</t>
         </is>
       </c>
     </row>
@@ -4444,12 +4444,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4459,26 +4459,26 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>(0, 1, 2, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>245.76</v>
+        <v>659.1799999999999</v>
       </c>
       <c r="G88" t="n">
-        <v>237.75</v>
+        <v>611.11</v>
       </c>
       <c r="H88" t="n">
-        <v>1.01</v>
+        <v>3.93</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>[21923.95, 25056.75, 24620.14]</t>
+          <t>[11522.01, 12360.18, 19364.87]</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>[22208.3, 24907.0, 24341.0]</t>
+          <t>[11950.3, 12804.8, 20325.3]</t>
         </is>
       </c>
     </row>
@@ -4490,12 +4490,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4505,26 +4505,26 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>(0, 1, 2, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>322.89</v>
+        <v>415.14</v>
       </c>
       <c r="G89" t="n">
-        <v>261.64</v>
+        <v>386.38</v>
       </c>
       <c r="H89" t="n">
-        <v>1.07</v>
+        <v>2.03</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>[25234.37, 24794.42, 15461.63]</t>
+          <t>[12618.84, 19771.96, 21546.76]</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>[24907.0, 24341.0, 15457.5]</t>
+          <t>[12804.8, 20325.3, 21966.6]</t>
         </is>
       </c>
     </row>
@@ -4536,12 +4536,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4551,26 +4551,26 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>180.04</v>
+        <v>321.22</v>
       </c>
       <c r="G90" t="n">
-        <v>149.15</v>
+        <v>315.44</v>
       </c>
       <c r="H90" t="n">
-        <v>0.75</v>
+        <v>1.36</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>[24626.91, 15341.69, 14498.14]</t>
+          <t>[19935.48, 21725.36, 29112.84]</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>[24341.0, 15457.5, 14452.4]</t>
+          <t>[20325.3, 21966.6, 29428.1]</t>
         </is>
       </c>
     </row>
@@ -4582,12 +4582,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4597,26 +4597,26 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>482.76</v>
+        <v>91.81</v>
       </c>
       <c r="G91" t="n">
-        <v>355.42</v>
+        <v>55.25</v>
       </c>
       <c r="H91" t="n">
-        <v>2.04</v>
+        <v>0.24</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>[15244.59, 14406.33, 17463.51]</t>
+          <t>[21964.5, 29432.82, 22479.46]</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>[15457.5, 14452.4, 18270.8]</t>
+          <t>[21966.6, 29428.1, 22638.4]</t>
         </is>
       </c>
     </row>
@@ -4628,41 +4628,41 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>(0, 0, 1)</t>
+          <t>(1, 0, 2)</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(1, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>347.49</v>
+        <v>2552.74</v>
       </c>
       <c r="G92" t="n">
-        <v>327.6</v>
+        <v>2531.39</v>
       </c>
       <c r="H92" t="n">
-        <v>6.6</v>
+        <v>15.46</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>[3620.4, 6606.52, 9155.6]</t>
+          <t>[23082.18, 22200.69, 13264.59]</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>[3219.2, 6442.5, 8738.0]</t>
+          <t>[20199.8, 19579.4, 11174.1]</t>
         </is>
       </c>
     </row>
@@ -4674,41 +4674,41 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>(0, 0, 1)</t>
+          <t>(2, 1, 2)</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(1, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>538.89</v>
+        <v>1603.29</v>
       </c>
       <c r="G93" t="n">
-        <v>421.19</v>
+        <v>1547.92</v>
       </c>
       <c r="H93" t="n">
-        <v>3.13</v>
+        <v>12.16</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>[6425.87, 9145.26, 19672.09]</t>
+          <t>[21323.55, 13106.45, 10383.14]</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>[6442.5, 8738.0, 18832.4]</t>
+          <t>[19579.4, 11174.1, 9415.9]</t>
         </is>
       </c>
     </row>
@@ -4720,41 +4720,41 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>(0, 0, 1)</t>
+          <t>(2, 1, 2)</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>1223.32</v>
+        <v>1181.22</v>
       </c>
       <c r="G94" t="n">
-        <v>1051.74</v>
+        <v>1034.95</v>
       </c>
       <c r="H94" t="n">
-        <v>4.91</v>
+        <v>10.01</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>[9151.71, 19673.79, 36359.21]</t>
+          <t>[12877.72, 10505.0, 10024.52]</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>[8738.0, 18832.4, 34459.1]</t>
+          <t>[11174.1, 9415.9, 9712.4]</t>
         </is>
       </c>
     </row>
@@ -4766,41 +4766,41 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>(0, 0, 1)</t>
+          <t>(2, 1, 2)</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(1, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>2029.46</v>
+        <v>403.25</v>
       </c>
       <c r="G95" t="n">
-        <v>1804.63</v>
+        <v>307.08</v>
       </c>
       <c r="H95" t="n">
-        <v>5.39</v>
+        <v>3.39</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>[19458.33, 36352.01, 42202.04]</t>
+          <t>[10069.88, 9956.54, 3188.09]</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>[18832.4, 34459.1, 39307.0]</t>
+          <t>[9415.9, 9712.4, 3211.2]</t>
         </is>
       </c>
     </row>
@@ -4812,41 +4812,41 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>(0, 0, 1)</t>
+          <t>(2, 1, 2)</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(1, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>2963.31</v>
+        <v>509.81</v>
       </c>
       <c r="G96" t="n">
-        <v>2808.21</v>
+        <v>317.17</v>
       </c>
       <c r="H96" t="n">
-        <v>8.85</v>
+        <v>5.11</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>[36069.09, 42198.62, 30951.61]</t>
+          <t>[9703.09, 3149.85, 5728.26]</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>[34459.1, 39307.0, 27028.6]</t>
+          <t>[9712.4, 3211.2, 6609.1]</t>
         </is>
       </c>
     </row>
@@ -4858,41 +4858,41 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>(0, 0, 1)</t>
+          <t>(2, 1, 2)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(1, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>3584.98</v>
+        <v>892.04</v>
       </c>
       <c r="G97" t="n">
-        <v>3500.92</v>
+        <v>736.05</v>
       </c>
       <c r="H97" t="n">
-        <v>13.76</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>[41726.53, 30942.11, 24369.53]</t>
+          <t>[3154.23, 5720.86, 7804.36]</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>[39307.0, 27028.6, 20199.8]</t>
+          <t>[3211.2, 6609.1, 9067.3]</t>
         </is>
       </c>
     </row>
@@ -4904,41 +4904,41 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>(1, 0, 4)</t>
+          <t>(2, 1, 2)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>(2, 1, 0, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>2517.05</v>
+        <v>1693.16</v>
       </c>
       <c r="G98" t="n">
-        <v>2437.97</v>
+        <v>1516.12</v>
       </c>
       <c r="H98" t="n">
-        <v>11.56</v>
+        <v>12.83</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>[28591.18, 23189.65, 22340.89]</t>
+          <t>[5794.81, 7895.13, 16780.59]</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>[27028.6, 20199.8, 19579.4]</t>
+          <t>[6609.1, 9067.3, 19342.5]</t>
         </is>
       </c>
     </row>
@@ -4950,17 +4950,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>(1, 0, 2)</t>
+          <t>(2, 1, 2)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -4969,22 +4969,22 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>2552.74</v>
+        <v>3354.01</v>
       </c>
       <c r="G99" t="n">
-        <v>2531.39</v>
+        <v>2908.05</v>
       </c>
       <c r="H99" t="n">
-        <v>15.46</v>
+        <v>13</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>[23082.18, 22200.69, 13264.59]</t>
+          <t>[8079.61, 16667.19, 30360.63]</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>[20199.8, 19579.4, 11174.1]</t>
+          <t>[9067.3, 19342.5, 35421.8]</t>
         </is>
       </c>
     </row>
@@ -4996,17 +4996,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>(2, 1, 2)</t>
+          <t>(1, 1, 4)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -5015,22 +5015,22 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>1603.29</v>
+        <v>4516.16</v>
       </c>
       <c r="G100" t="n">
-        <v>1547.92</v>
+        <v>4307.4</v>
       </c>
       <c r="H100" t="n">
-        <v>12.16</v>
+        <v>13.44</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>[21323.55, 13106.45, 10383.14]</t>
+          <t>[16953.52, 30102.56, 35031.91]</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>[19579.4, 11174.1, 9415.9]</t>
+          <t>[19342.5, 35421.8, 40245.9]</t>
         </is>
       </c>
     </row>
@@ -5042,17 +5042,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>(2, 1, 2)</t>
+          <t>(2, 1, 1)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -5061,22 +5061,22 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>1181.22</v>
+        <v>3078.83</v>
       </c>
       <c r="G101" t="n">
-        <v>1034.95</v>
+        <v>2911.35</v>
       </c>
       <c r="H101" t="n">
-        <v>10.01</v>
+        <v>8.15</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>[12877.72, 10505.0, 10024.52]</t>
+          <t>[32122.78, 36348.48, 26596.88]</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>[11174.1, 9415.9, 9712.4]</t>
+          <t>[35421.8, 40245.9, 28134.5]</t>
         </is>
       </c>
     </row>
@@ -5088,12 +5088,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5103,26 +5103,26 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>2335.9</v>
+        <v>1403.34</v>
       </c>
       <c r="G102" t="n">
-        <v>2062.99</v>
+        <v>1073.49</v>
       </c>
       <c r="H102" t="n">
-        <v>22.58</v>
+        <v>5.09</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>[3365.85, 5562.96, 12672.03]</t>
+          <t>[18920.64, 21056.63, 13447.84]</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>[4432.0, 7097.0, 16260.8]</t>
+          <t>[18272.4, 23386.7, 13690.0]</t>
         </is>
       </c>
     </row>
@@ -5134,12 +5134,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -5153,22 +5153,22 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>595.38</v>
+        <v>1673.54</v>
       </c>
       <c r="G103" t="n">
-        <v>556.4299999999999</v>
+        <v>1299.11</v>
       </c>
       <c r="H103" t="n">
-        <v>4.18</v>
+        <v>6.85</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>[6809.7, 15683.62, 15438.98]</t>
+          <t>[20595.75, 13156.87, 11541.77]</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>[7097.0, 16260.8, 16243.8]</t>
+          <t>[23386.7, 13690.0, 12115.0]</t>
         </is>
       </c>
     </row>
@@ -5180,12 +5180,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5199,22 +5199,22 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>242.3</v>
+        <v>637.4400000000001</v>
       </c>
       <c r="G104" t="n">
-        <v>208.19</v>
+        <v>590.03</v>
       </c>
       <c r="H104" t="n">
-        <v>1.21</v>
+        <v>3.65</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>[16118.97, 15861.9, 24505.06]</t>
+          <t>[14198.77, 12458.72, 20001.09]</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>[16260.8, 16243.8, 24404.2]</t>
+          <t>[13690.0, 12115.0, 20918.7]</t>
         </is>
       </c>
     </row>
@@ -5226,12 +5226,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5245,22 +5245,22 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>1088.33</v>
+        <v>832.8200000000001</v>
       </c>
       <c r="G105" t="n">
-        <v>794.5</v>
+        <v>626.9400000000001</v>
       </c>
       <c r="H105" t="n">
-        <v>2.86</v>
+        <v>5.75</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>[15949.77, 24647.7, 30140.33]</t>
+          <t>[12177.25, 19549.36, 3964.27]</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>[16243.8, 24404.2, 31986.3]</t>
+          <t>[12115.0, 20918.7, 4413.5]</t>
         </is>
       </c>
     </row>
@@ -5272,12 +5272,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5291,22 +5291,22 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>1552.59</v>
+        <v>936</v>
       </c>
       <c r="G106" t="n">
-        <v>1399.45</v>
+        <v>832.61</v>
       </c>
       <c r="H106" t="n">
-        <v>5.54</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>[24935.14, 30487.86, 20066.43]</t>
+          <t>[19487.14, 3952.74, 6439.68]</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>[24404.2, 31986.3, 22235.4]</t>
+          <t>[20918.7, 4413.5, 7045.2]</t>
         </is>
       </c>
     </row>
@@ -5318,12 +5318,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5337,22 +5337,22 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>1865.09</v>
+        <v>604.96</v>
       </c>
       <c r="G107" t="n">
-        <v>1757.98</v>
+        <v>517.6799999999999</v>
       </c>
       <c r="H107" t="n">
-        <v>7.34</v>
+        <v>5.54</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>[30081.46, 19798.58, 17340.12]</t>
+          <t>[4132.76, 6732.91, 15478.5]</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>[31986.3, 22235.4, 18272.4]</t>
+          <t>[4413.5, 7045.2, 16438.5]</t>
         </is>
       </c>
     </row>
@@ -5364,12 +5364,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5383,22 +5383,22 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>2116.75</v>
+        <v>389.73</v>
       </c>
       <c r="G108" t="n">
-        <v>1725.46</v>
+        <v>304.75</v>
       </c>
       <c r="H108" t="n">
-        <v>7.6</v>
+        <v>1.9</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>[20571.51, 18016.93, 20129.69]</t>
+          <t>[7023.54, 16160.79, 15978.42]</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>[22235.4, 18272.4, 23386.7]</t>
+          <t>[7045.2, 16438.5, 16593.3]</t>
         </is>
       </c>
     </row>
@@ -5410,12 +5410,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5429,22 +5429,22 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>1403.34</v>
+        <v>460.24</v>
       </c>
       <c r="G109" t="n">
-        <v>1073.49</v>
+        <v>437.64</v>
       </c>
       <c r="H109" t="n">
-        <v>5.09</v>
+        <v>2.31</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>[18920.64, 21056.63, 13447.84]</t>
+          <t>[16194.42, 16010.57, 24522.28]</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>[18272.4, 23386.7, 13690.0]</t>
+          <t>[16438.5, 16593.3, 25008.4]</t>
         </is>
       </c>
     </row>
@@ -5456,12 +5456,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5475,22 +5475,22 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>1673.54</v>
+        <v>1251.45</v>
       </c>
       <c r="G110" t="n">
-        <v>1299.11</v>
+        <v>931.05</v>
       </c>
       <c r="H110" t="n">
-        <v>6.85</v>
+        <v>3.33</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>[20595.75, 13156.87, 11541.77]</t>
+          <t>[16160.42, 24757.13, 30942.3]</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>[23386.7, 13690.0, 12115.0]</t>
+          <t>[16593.3, 25008.4, 33051.3]</t>
         </is>
       </c>
     </row>
@@ -5502,12 +5502,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5521,22 +5521,22 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>637.4400000000001</v>
+        <v>1103.65</v>
       </c>
       <c r="G111" t="n">
-        <v>590.03</v>
+        <v>932.8099999999999</v>
       </c>
       <c r="H111" t="n">
-        <v>3.65</v>
+        <v>3.39</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>[14198.77, 12458.72, 20001.09]</t>
+          <t>[25171.11, 31455.82, 21074.07]</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>[13690.0, 12115.0, 20918.7]</t>
+          <t>[25008.4, 33051.3, 22114.3]</t>
         </is>
       </c>
     </row>
@@ -5548,12 +5548,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5563,26 +5563,26 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>5133.89</v>
+        <v>1164.47</v>
       </c>
       <c r="G112" t="n">
-        <v>5109.75</v>
+        <v>1162.39</v>
       </c>
       <c r="H112" t="n">
-        <v>40.13</v>
+        <v>9.35</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>[6637.81, 7949.0, 8268.65]</t>
+          <t>[12258.22, 11689.77, 10167.75]</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>[11065.4, 13251.6, 13867.7]</t>
+          <t>[13406.8, 12774.7, 11421.4]</t>
         </is>
       </c>
     </row>
@@ -5594,12 +5594,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5613,22 +5613,22 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>2246.6</v>
+        <v>849.1900000000001</v>
       </c>
       <c r="G113" t="n">
-        <v>2190.85</v>
+        <v>838.1</v>
       </c>
       <c r="H113" t="n">
-        <v>14.24</v>
+        <v>8.24</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>[10380.55, 12172.27, 20753.44]</t>
+          <t>[11964.06, 10735.43, 7218.72]</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>[13251.6, 13867.7, 22759.5]</t>
+          <t>[12774.7, 11421.4, 8236.4]</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5659,22 +5659,22 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>1250.95</v>
+        <v>580.3099999999999</v>
       </c>
       <c r="G114" t="n">
-        <v>1224.38</v>
+        <v>569.27</v>
       </c>
       <c r="H114" t="n">
-        <v>6.24</v>
+        <v>6.02</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>[13005.32, 24184.21, 23562.55]</t>
+          <t>[10906.4, 7510.31, 9373.07]</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>[13867.7, 22759.5, 22176.5]</t>
+          <t>[11421.4, 8236.4, 9839.8]</t>
         </is>
       </c>
     </row>
@@ -5686,12 +5686,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -5705,22 +5705,22 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>4054.24</v>
+        <v>1548.23</v>
       </c>
       <c r="G115" t="n">
-        <v>3500.15</v>
+        <v>1148.49</v>
       </c>
       <c r="H115" t="n">
-        <v>11.01</v>
+        <v>10.34</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>[24561.57, 24496.87, 49957.6]</t>
+          <t>[7594.41, 9631.6, 9701.41]</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>[22759.5, 22176.5, 43579.6]</t>
+          <t>[8236.4, 9839.8, 12296.7]</t>
         </is>
       </c>
     </row>
@@ -5732,12 +5732,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -5751,22 +5751,22 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>2726.11</v>
+        <v>1758.52</v>
       </c>
       <c r="G116" t="n">
-        <v>2436.45</v>
+        <v>1446.26</v>
       </c>
       <c r="H116" t="n">
-        <v>7.81</v>
+        <v>10.84</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>[24055.28, 47712.58, 25021.2]</t>
+          <t>[9807.51, 10183.43, 12415.28]</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>[22176.5, 43579.6, 23723.6]</t>
+          <t>[9839.8, 12296.7, 14608.5]</t>
         </is>
       </c>
     </row>
@@ -5778,12 +5778,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -5797,22 +5797,22 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>1916.63</v>
+        <v>2318.99</v>
       </c>
       <c r="G117" t="n">
-        <v>1346.66</v>
+        <v>2306.46</v>
       </c>
       <c r="H117" t="n">
-        <v>4.31</v>
+        <v>16.32</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>[46830.93, 23855.04, 12749.59]</t>
+          <t>[10190.93, 12439.79, 12926.19]</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>[43579.6, 23723.6, 13406.8]</t>
+          <t>[12296.7, 14608.5, 15571.1]</t>
         </is>
       </c>
     </row>
@@ -5824,12 +5824,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5843,22 +5843,22 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>965.74</v>
+        <v>1384.64</v>
       </c>
       <c r="G118" t="n">
-        <v>865.02</v>
+        <v>1368.91</v>
       </c>
       <c r="H118" t="n">
-        <v>6.32</v>
+        <v>7.83</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>[23465.76, 12228.72, 11615.56]</t>
+          <t>[13006.18, 14474.26, 24257.64]</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>[23723.6, 13406.8, 12774.7]</t>
+          <t>[14608.5, 15571.1, 25665.2]</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -5889,22 +5889,22 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>1164.47</v>
+        <v>527.36</v>
       </c>
       <c r="G119" t="n">
-        <v>1162.39</v>
+        <v>510.4</v>
       </c>
       <c r="H119" t="n">
-        <v>9.35</v>
+        <v>2.58</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>[12258.22, 11689.77, 10167.75]</t>
+          <t>[14890.25, 26022.46, 25355.89]</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>[13406.8, 12774.7, 11421.4]</t>
+          <t>[15571.1, 25665.2, 24862.8]</t>
         </is>
       </c>
     </row>
@@ -5916,12 +5916,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -5935,22 +5935,22 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>849.1900000000001</v>
+        <v>2214.73</v>
       </c>
       <c r="G120" t="n">
-        <v>838.1</v>
+        <v>1811.74</v>
       </c>
       <c r="H120" t="n">
-        <v>8.24</v>
+        <v>4.92</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>[11964.06, 10735.43, 7218.72]</t>
+          <t>[26318.32, 26059.22, 51941.07]</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>[12774.7, 11421.4, 8236.4]</t>
+          <t>[25665.2, 24862.8, 48355.4]</t>
         </is>
       </c>
     </row>
@@ -5962,12 +5962,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -5981,22 +5981,22 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>580.3099999999999</v>
+        <v>2448.46</v>
       </c>
       <c r="G121" t="n">
-        <v>569.27</v>
+        <v>2280.98</v>
       </c>
       <c r="H121" t="n">
-        <v>6.02</v>
+        <v>7.43</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>[10906.4, 7510.31, 9373.07]</t>
+          <t>[25892.24, 51146.64, 27456.67]</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>[11421.4, 8236.4, 9839.8]</t>
+          <t>[24862.8, 48355.4, 24434.4]</t>
         </is>
       </c>
     </row>
@@ -6008,17 +6008,17 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>(0, 1, 0)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -6027,22 +6027,22 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>1683.62</v>
+        <v>31.96</v>
       </c>
       <c r="G122" t="n">
-        <v>1672.25</v>
+        <v>27.18</v>
       </c>
       <c r="H122" t="n">
-        <v>54.92</v>
+        <v>0.63</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>[4465.08, 4496.11, 5164.77]</t>
+          <t>[4368.82, 4406.06, 4229.64]</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>[2911.0, 2981.0, 3217.2]</t>
+          <t>[4363.4, 4359.7, 4199.9]</t>
         </is>
       </c>
     </row>
@@ -6054,17 +6054,17 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>(1, 1, 0)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -6073,22 +6073,22 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>376.37</v>
+        <v>44.13</v>
       </c>
       <c r="G123" t="n">
-        <v>371.92</v>
+        <v>42.1</v>
       </c>
       <c r="H123" t="n">
-        <v>11.4</v>
+        <v>0.97</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>[3281.33, 3658.82, 3966.4]</t>
+          <t>[4401.98, 4225.72, 4466.72]</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>[2981.0, 3217.2, 3592.6]</t>
+          <t>[4359.7, 4199.9, 4408.5]</t>
         </is>
       </c>
     </row>
@@ -6100,12 +6100,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -6119,22 +6119,22 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>158.01</v>
+        <v>5366.58</v>
       </c>
       <c r="G124" t="n">
-        <v>149.26</v>
+        <v>3108.61</v>
       </c>
       <c r="H124" t="n">
-        <v>4.32</v>
+        <v>55.11</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>[3439.47, 3699.45, 3968.25]</t>
+          <t>[4195.36, 4434.63, 14941.75]</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>[3217.2, 3592.6, 3849.6]</t>
+          <t>[4199.9, 4408.5, 5646.6]</t>
         </is>
       </c>
     </row>
@@ -6146,12 +6146,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -6165,22 +6165,22 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>113.17</v>
+        <v>5373.56</v>
       </c>
       <c r="G125" t="n">
-        <v>104.61</v>
+        <v>3114.24</v>
       </c>
       <c r="H125" t="n">
-        <v>2.61</v>
+        <v>55.23</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>[3519.18, 3774.88, 4135.52]</t>
+          <t>[4438.22, 14953.84, 3005.97]</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>[3592.6, 3849.6, 4301.2]</t>
+          <t>[4408.5, 5646.6, 3000.2]</t>
         </is>
       </c>
     </row>
@@ -6192,41 +6192,41 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>92.53</v>
+        <v>8336.030000000001</v>
       </c>
       <c r="G126" t="n">
-        <v>80.15000000000001</v>
+        <v>5103.35</v>
       </c>
       <c r="H126" t="n">
-        <v>1.88</v>
+        <v>94.93000000000001</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>[3833.6, 4199.86, 4186.79]</t>
+          <t>[20071.44, 3455.34, 3466.27]</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>[3849.6, 4301.2, 4309.9]</t>
+          <t>[5646.6, 3000.2, 3036.2]</t>
         </is>
       </c>
     </row>
@@ -6238,12 +6238,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -6253,26 +6253,26 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>98.19</v>
+        <v>1341.67</v>
       </c>
       <c r="G127" t="n">
-        <v>97.76000000000001</v>
+        <v>1341.61</v>
       </c>
       <c r="H127" t="n">
-        <v>2.26</v>
+        <v>43.64</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>[4212.95, 4199.84, 4268.44]</t>
+          <t>[1655.15, 1680.76, 1871.37]</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>[4301.2, 4309.9, 4363.4]</t>
+          <t>[3000.2, 3036.2, 3195.7]</t>
         </is>
       </c>
     </row>
@@ -6284,12 +6284,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -6299,26 +6299,26 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>31.28</v>
+        <v>360.76</v>
       </c>
       <c r="G128" t="n">
-        <v>28.39</v>
+        <v>353.87</v>
       </c>
       <c r="H128" t="n">
-        <v>0.65</v>
+        <v>10.88</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>[4265.4, 4335.07, 4372.02]</t>
+          <t>[2605.25, 2934.46, 3231.68]</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>[4309.9, 4363.4, 4359.7]</t>
+          <t>[3036.2, 3195.7, 3601.1]</t>
         </is>
       </c>
     </row>
@@ -6330,12 +6330,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -6345,26 +6345,26 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>31.96</v>
+        <v>82.59</v>
       </c>
       <c r="G129" t="n">
-        <v>27.18</v>
+        <v>66.62</v>
       </c>
       <c r="H129" t="n">
-        <v>0.63</v>
+        <v>1.77</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>[4368.82, 4406.06, 4229.64]</t>
+          <t>[3196.95, 3521.01, 3768.88]</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>[4363.4, 4359.7, 4199.9]</t>
+          <t>[3195.7, 3601.1, 3887.4]</t>
         </is>
       </c>
     </row>
@@ -6376,12 +6376,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -6391,26 +6391,26 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>44.13</v>
+        <v>340.38</v>
       </c>
       <c r="G130" t="n">
-        <v>42.1</v>
+        <v>257.1</v>
       </c>
       <c r="H130" t="n">
-        <v>0.97</v>
+        <v>5.77</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>[4401.98, 4225.72, 4466.72]</t>
+          <t>[3520.56, 3768.42, 4182.52]</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>[4359.7, 4199.9, 4408.5]</t>
+          <t>[3601.1, 3887.4, 4754.3]</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6437,26 +6437,26 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>5366.58</v>
+        <v>402.44</v>
       </c>
       <c r="G131" t="n">
-        <v>3108.61</v>
+        <v>350.45</v>
       </c>
       <c r="H131" t="n">
-        <v>55.11</v>
+        <v>7.53</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>[4195.36, 4434.63, 14941.75]</t>
+          <t>[3814.31, 4233.38, 4225.54]</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>[4199.9, 4408.5, 5646.6]</t>
+          <t>[3887.4, 4754.3, 4682.9]</t>
         </is>
       </c>
     </row>
@@ -6468,17 +6468,17 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>(0, 1, 0)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -6493,11 +6493,11 @@
         <v>0</v>
       </c>
       <c r="H132" t="n">
-        <v>9.768214367397694e+16</v>
+        <v>0</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>[-0.0, -0.0, -0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -6514,17 +6514,17 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>(0, 1, 0)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -6539,11 +6539,11 @@
         <v>0</v>
       </c>
       <c r="H133" t="n">
-        <v>4.635596388947347e+16</v>
+        <v>400</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[-0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -6560,12 +6560,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -6585,7 +6585,7 @@
         <v>0</v>
       </c>
       <c r="H134" t="n">
-        <v>6.524335458900721e+17</v>
+        <v>0</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
@@ -6606,12 +6606,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -6631,11 +6631,11 @@
         <v>0</v>
       </c>
       <c r="H135" t="n">
-        <v>4.343062490682627e+17</v>
+        <v>300</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, -0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -6652,12 +6652,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -6677,11 +6677,11 @@
         <v>0</v>
       </c>
       <c r="H136" t="n">
-        <v>3.329087389628494e+17</v>
+        <v>133.33</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>[0.0, -0.0, -0.0]</t>
+          <t>[0.0, -0.0, 0.0]</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -6723,7 +6723,7 @@
         <v>0</v>
       </c>
       <c r="H137" t="n">
-        <v>2.361109400693341e+17</v>
+        <v>400</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
@@ -6744,12 +6744,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -6769,11 +6769,11 @@
         <v>0</v>
       </c>
       <c r="H138" t="n">
-        <v>2011333.33</v>
+        <v>133.33</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[-0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -6790,12 +6790,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -6836,12 +6836,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -6861,11 +6861,11 @@
         <v>0</v>
       </c>
       <c r="H140" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>[-0.0, -0.0, -0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -6882,12 +6882,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -6907,11 +6907,11 @@
         <v>0</v>
       </c>
       <c r="H141" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[-0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -6928,41 +6928,41 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(0, 1, 0)</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>7234.36</v>
+        <v>401.1</v>
       </c>
       <c r="G142" t="n">
-        <v>6487.08</v>
+        <v>291.14</v>
       </c>
       <c r="H142" t="n">
-        <v>58.41</v>
+        <v>1.12</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>[18545.41, 20652.14, 22519.3]</t>
+          <t>[32344.76, 30681.06, 24192.59]</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>[9299.7, 12434.2, 20521.7]</t>
+          <t>[32329.0, 30870.5, 24860.8]</t>
         </is>
       </c>
     </row>
@@ -6974,41 +6974,41 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(0, 1, 0)</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>8032.9</v>
+        <v>409.97</v>
       </c>
       <c r="G143" t="n">
-        <v>6915.66</v>
+        <v>297.25</v>
       </c>
       <c r="H143" t="n">
-        <v>31.66</v>
+        <v>1.14</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>[10952.79, 12592.82, 14184.11]</t>
+          <t>[30666.11, 24180.8, 19969.15]</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>[12434.2, 20521.7, 25520.8]</t>
+          <t>[30870.5, 24860.8, 19961.8]</t>
         </is>
       </c>
     </row>
@@ -7020,41 +7020,41 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(0, 1, 0)</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>9512.059999999999</v>
+        <v>337.38</v>
       </c>
       <c r="G144" t="n">
-        <v>9236.459999999999</v>
+        <v>296.18</v>
       </c>
       <c r="H144" t="n">
-        <v>36.18</v>
+        <v>1.39</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>[14227.86, 15933.91, 17524.95]</t>
+          <t>[24341.97, 20102.24, 16506.35]</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>[20521.7, 25520.8, 29353.6]</t>
+          <t>[24860.8, 19961.8, 16735.6]</t>
         </is>
       </c>
     </row>
@@ -7066,41 +7066,41 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(0, 1, 0)</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>9519.799999999999</v>
+        <v>347.51</v>
       </c>
       <c r="G145" t="n">
-        <v>8091.45</v>
+        <v>281.71</v>
       </c>
       <c r="H145" t="n">
-        <v>23.68</v>
+        <v>1.73</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>[22126.02, 23516.92, 24707.32]</t>
+          <t>[20530.71, 16858.17, 9663.45]</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>[25520.8, 29353.6, 39750.2]</t>
+          <t>[19961.8, 16735.6, 9509.8]</t>
         </is>
       </c>
     </row>
@@ -7112,41 +7112,41 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(0, 1, 0)</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>8147.32</v>
+        <v>214.07</v>
       </c>
       <c r="G146" t="n">
-        <v>7121.15</v>
+        <v>178.13</v>
       </c>
       <c r="H146" t="n">
-        <v>19.59</v>
+        <v>1.29</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>[26530.25, 27373.91, 28074.28]</t>
+          <t>[16391.03, 9395.67, 12562.52]</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>[29353.6, 39750.2, 34238.1]</t>
+          <t>[16735.6, 9509.8, 12638.2]</t>
         </is>
       </c>
     </row>
@@ -7158,17 +7158,17 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(0, 1, 0)</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -7177,22 +7177,22 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>302.84</v>
+        <v>181.29</v>
       </c>
       <c r="G147" t="n">
-        <v>292.94</v>
+        <v>169.58</v>
       </c>
       <c r="H147" t="n">
-        <v>0.85</v>
+        <v>1.17</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>[39554.98, 34621.0, 32629.69]</t>
+          <t>[9593.19, 12826.61, 21169.34]</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>[39750.2, 34238.1, 32329.0]</t>
+          <t>[9509.8, 12638.2, 20932.4]</t>
         </is>
       </c>
     </row>
@@ -7204,12 +7204,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -7223,22 +7223,22 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>565.33</v>
+        <v>54.06</v>
       </c>
       <c r="G148" t="n">
-        <v>553.1900000000001</v>
+        <v>45.66</v>
       </c>
       <c r="H148" t="n">
-        <v>1.69</v>
+        <v>0.3</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>[34883.43, 32954.4, 31259.34]</t>
+          <t>[12715.12, 20985.33, 26097.37]</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>[34238.1, 32329.0, 30870.5]</t>
+          <t>[12638.2, 20932.4, 26104.5]</t>
         </is>
       </c>
     </row>
@@ -7250,12 +7250,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -7269,22 +7269,22 @@
         </is>
       </c>
       <c r="F149" t="n">
-        <v>401.1</v>
+        <v>151.91</v>
       </c>
       <c r="G149" t="n">
-        <v>291.14</v>
+        <v>143.37</v>
       </c>
       <c r="H149" t="n">
-        <v>1.12</v>
+        <v>0.54</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>[32344.76, 30681.06, 24192.59]</t>
+          <t>[20858.39, 25939.5, 29835.19]</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>[32329.0, 30870.5, 24860.8]</t>
+          <t>[20932.4, 26104.5, 30026.3]</t>
         </is>
       </c>
     </row>
@@ -7296,12 +7296,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -7315,22 +7315,22 @@
         </is>
       </c>
       <c r="F150" t="n">
-        <v>409.97</v>
+        <v>1642.73</v>
       </c>
       <c r="G150" t="n">
-        <v>297.25</v>
+        <v>1000.43</v>
       </c>
       <c r="H150" t="n">
-        <v>1.14</v>
+        <v>2.37</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>[30666.11, 24180.8, 19969.15]</t>
+          <t>[26031.55, 29941.05, 40545.72]</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>[30870.5, 24860.8, 19961.8]</t>
+          <t>[26104.5, 30026.3, 43388.8]</t>
         </is>
       </c>
     </row>
@@ -7342,12 +7342,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -7361,22 +7361,22 @@
         </is>
       </c>
       <c r="F151" t="n">
-        <v>337.38</v>
+        <v>2103.84</v>
       </c>
       <c r="G151" t="n">
-        <v>296.18</v>
+        <v>1715</v>
       </c>
       <c r="H151" t="n">
-        <v>1.39</v>
+        <v>4.25</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>[24341.97, 20102.24, 16506.35]</t>
+          <t>[30024.96, 40659.35, 35021.18]</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>[24860.8, 19961.8, 16735.6]</t>
+          <t>[30026.3, 43388.8, 37435.4]</t>
         </is>
       </c>
     </row>
@@ -7388,41 +7388,41 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(0, 1, 0)</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>6437.48</v>
+        <v>394.55</v>
       </c>
       <c r="G152" t="n">
-        <v>5989.76</v>
+        <v>386.02</v>
       </c>
       <c r="H152" t="n">
-        <v>56.44</v>
+        <v>1.81</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>[15707.73, 18549.73, 20031.83]</t>
+          <t>[21287.55, 25623.06, 18942.25]</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>[10557.7, 9344.2, 16418.1]</t>
+          <t>[20792.5, 25258.8, 18643.5]</t>
         </is>
       </c>
     </row>
@@ -7434,41 +7434,41 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(0, 1, 0)</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>2231.79</v>
+        <v>177</v>
       </c>
       <c r="G153" t="n">
-        <v>2153.57</v>
+        <v>171.89</v>
       </c>
       <c r="H153" t="n">
-        <v>14.46</v>
+        <v>0.87</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>[10872.67, 14422.58, 16815.57]</t>
+          <t>[25027.18, 18501.74, 15352.62]</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>[9344.2, 16418.1, 19752.3]</t>
+          <t>[25258.8, 18643.5, 15494.9]</t>
         </is>
       </c>
     </row>
@@ -7480,41 +7480,41 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(0, 1, 0)</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>4277.49</v>
+        <v>26.62</v>
       </c>
       <c r="G154" t="n">
-        <v>4038.03</v>
+        <v>21.71</v>
       </c>
       <c r="H154" t="n">
-        <v>22.31</v>
+        <v>0.13</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>[11629.19, 14488.46, 16474.76]</t>
+          <t>[18672.97, 15494.7, 14596.25]</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>[16418.1, 19752.3, 18536.1]</t>
+          <t>[18643.5, 15494.9, 14631.7]</t>
         </is>
       </c>
     </row>
@@ -7526,41 +7526,41 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(0, 1, 0)</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>3847.14</v>
+        <v>80.22</v>
       </c>
       <c r="G155" t="n">
-        <v>3791.51</v>
+        <v>68.92</v>
       </c>
       <c r="H155" t="n">
-        <v>17.68</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>[23156.92, 21796.32, 21163.22]</t>
+          <t>[15470.25, 14573.21, 10823.59]</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>[19752.3, 18536.1, 25872.9]</t>
+          <t>[15494.9, 14631.7, 10947.2]</t>
         </is>
       </c>
     </row>
@@ -7572,41 +7572,41 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(0, 1, 0)</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>4152.26</v>
+        <v>144.19</v>
       </c>
       <c r="G156" t="n">
-        <v>3139.59</v>
+        <v>121.61</v>
       </c>
       <c r="H156" t="n">
-        <v>13.04</v>
+        <v>1.16</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>[17659.37, 18911.91, 19537.56]</t>
+          <t>[14596.43, 10840.84, 9594.8]</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>[18536.1, 25872.9, 21118.6]</t>
+          <t>[14631.7, 10947.2, 9818.0]</t>
         </is>
       </c>
     </row>
@@ -7618,17 +7618,17 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(0, 1, 0)</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -7637,22 +7637,22 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>302.18</v>
+        <v>134.11</v>
       </c>
       <c r="G157" t="n">
-        <v>234.18</v>
+        <v>122.31</v>
       </c>
       <c r="H157" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>[25668.01, 20637.25, 20776.2]</t>
+          <t>[10867.04, 9617.98, 16899.14]</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>[25872.9, 21118.6, 20792.5]</t>
+          <t>[10947.2, 9818.0, 16812.4]</t>
         </is>
       </c>
     </row>
@@ -7664,12 +7664,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -7683,22 +7683,22 @@
         </is>
       </c>
       <c r="F158" t="n">
-        <v>204.24</v>
+        <v>404.25</v>
       </c>
       <c r="G158" t="n">
-        <v>169.02</v>
+        <v>331.8</v>
       </c>
       <c r="H158" t="n">
-        <v>0.8</v>
+        <v>1.96</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>[20830.17, 20996.82, 25273.11]</t>
+          <t>[9688.93, 17023.8, 20481.01]</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>[21118.6, 20792.5, 25258.8]</t>
+          <t>[9818.0, 16812.4, 19826.1]</t>
         </is>
       </c>
     </row>
@@ -7710,12 +7710,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -7729,22 +7729,22 @@
         </is>
       </c>
       <c r="F159" t="n">
-        <v>394.55</v>
+        <v>622.04</v>
       </c>
       <c r="G159" t="n">
-        <v>386.02</v>
+        <v>564.9</v>
       </c>
       <c r="H159" t="n">
-        <v>1.81</v>
+        <v>3</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>[21287.55, 25623.06, 18942.25]</t>
+          <t>[17250.58, 20753.85, 19475.98]</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>[20792.5, 25258.8, 18643.5]</t>
+          <t>[16812.4, 19826.1, 19147.2]</t>
         </is>
       </c>
     </row>
@@ -7756,12 +7756,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -7775,22 +7775,22 @@
         </is>
       </c>
       <c r="F160" t="n">
-        <v>177</v>
+        <v>706.73</v>
       </c>
       <c r="G160" t="n">
-        <v>171.89</v>
+        <v>570.41</v>
       </c>
       <c r="H160" t="n">
-        <v>0.87</v>
+        <v>2.34</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>[25027.18, 18501.74, 15352.62]</t>
+          <t>[20226.67, 18981.27, 26494.27]</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>[25258.8, 18643.5, 15494.9]</t>
+          <t>[19826.1, 19147.2, 27639.0]</t>
         </is>
       </c>
     </row>
@@ -7802,12 +7802,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -7821,22 +7821,22 @@
         </is>
       </c>
       <c r="F161" t="n">
-        <v>26.62</v>
+        <v>1054.57</v>
       </c>
       <c r="G161" t="n">
-        <v>21.71</v>
+        <v>905.66</v>
       </c>
       <c r="H161" t="n">
-        <v>0.13</v>
+        <v>3.73</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>[18672.97, 15494.7, 14596.25]</t>
+          <t>[18605.36, 25969.57, 21197.5]</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>[18643.5, 15494.9, 14631.7]</t>
+          <t>[19147.2, 27639.0, 21703.2]</t>
         </is>
       </c>
     </row>
@@ -7848,41 +7848,41 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(2, 1, 0)</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>3948.33</v>
+        <v>1508.22</v>
       </c>
       <c r="G162" t="n">
-        <v>3706.47</v>
+        <v>1292.82</v>
       </c>
       <c r="H162" t="n">
-        <v>256.73</v>
+        <v>21.07</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>[6273.93, 6273.93, 6273.93]</t>
+          <t>[8653.29, 3395.44, 8632.04]</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>[932.7, 2505.8, 4263.9]</t>
+          <t>[7304.7, 3080.6, 6417.0]</t>
         </is>
       </c>
     </row>
@@ -7894,41 +7894,41 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(2, 1, 0)</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F163" t="n">
-        <v>2029.34</v>
+        <v>1144.81</v>
       </c>
       <c r="G163" t="n">
-        <v>1624.65</v>
+        <v>938.73</v>
       </c>
       <c r="H163" t="n">
-        <v>55.24</v>
+        <v>18.81</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>[5703.61, 5703.61, 5703.61]</t>
+          <t>[3216.17, 8157.66, 4716.25]</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>[2505.8, 4263.9, 5467.2]</t>
+          <t>[3080.6, 6417.0, 3776.3]</t>
         </is>
       </c>
     </row>
@@ -7940,41 +7940,41 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F164" t="n">
-        <v>1387.1</v>
+        <v>2531.73</v>
       </c>
       <c r="G164" t="n">
-        <v>1102.41</v>
+        <v>1759.13</v>
       </c>
       <c r="H164" t="n">
-        <v>18.78</v>
+        <v>29.22</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>[5484.54, 5484.54, 5484.54]</t>
+          <t>[10750.2, 4305.87, 7194.52]</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>[4263.9, 5467.2, 7553.8]</t>
+          <t>[6417.0, 3776.3, 6779.9]</t>
         </is>
       </c>
     </row>
@@ -7986,41 +7986,41 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F165" t="n">
-        <v>1295.82</v>
+        <v>81.81</v>
       </c>
       <c r="G165" t="n">
-        <v>990.53</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="H165" t="n">
-        <v>14.27</v>
+        <v>1.32</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>[5094.04, 5382.16, 5474.52]</t>
+          <t>[3848.97, 6901.53, 945.76]</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>[5467.2, 7553.8, 5901.3]</t>
+          <t>[3776.3, 6779.9, 943.6]</t>
         </is>
       </c>
     </row>
@@ -8032,41 +8032,41 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F166" t="n">
-        <v>2924.46</v>
+        <v>33.85</v>
       </c>
       <c r="G166" t="n">
-        <v>2342.7</v>
+        <v>27.37</v>
       </c>
       <c r="H166" t="n">
-        <v>26.23</v>
+        <v>0.79</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>[5517.35, 5532.92, 5537.74]</t>
+          <t>[6834.33, 936.55, 2516.16]</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>[7553.8, 5901.3, 10161.0]</t>
+          <t>[6779.9, 943.6, 2536.8]</t>
         </is>
       </c>
     </row>
@@ -8078,12 +8078,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -8097,22 +8097,22 @@
         </is>
       </c>
       <c r="F167" t="n">
-        <v>1142.26</v>
+        <v>725.03</v>
       </c>
       <c r="G167" t="n">
-        <v>949.96</v>
+        <v>598.97</v>
       </c>
       <c r="H167" t="n">
-        <v>12.26</v>
+        <v>20.65</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>[7086.1, 8578.69, 7221.92]</t>
+          <t>[1086.53, 3056.58, 5446.1]</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>[5901.3, 10161.0, 7304.7]</t>
+          <t>[943.6, 2536.8, 4311.9]</t>
         </is>
       </c>
     </row>
@@ -8124,12 +8124,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -8143,22 +8143,22 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>1466.36</v>
+        <v>881.38</v>
       </c>
       <c r="G168" t="n">
-        <v>1173.16</v>
+        <v>790.67</v>
       </c>
       <c r="H168" t="n">
-        <v>15.23</v>
+        <v>17.92</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>[7766.3, 6538.02, 2722.51]</t>
+          <t>[2861.08, 5082.12, 6802.33]</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>[10161.0, 7304.7, 3080.6]</t>
+          <t>[2536.8, 4311.9, 5524.8]</t>
         </is>
       </c>
     </row>
@@ -8170,17 +8170,17 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>(2, 1, 0)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -8189,22 +8189,22 @@
         </is>
       </c>
       <c r="F169" t="n">
-        <v>1508.22</v>
+        <v>1114.1</v>
       </c>
       <c r="G169" t="n">
-        <v>1292.82</v>
+        <v>1010.08</v>
       </c>
       <c r="H169" t="n">
-        <v>21.07</v>
+        <v>16.43</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>[8653.29, 3395.44, 8632.04]</t>
+          <t>[4810.64, 6422.65, 9239.94]</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>[7304.7, 3080.6, 6417.0]</t>
+          <t>[4311.9, 5524.8, 7606.3]</t>
         </is>
       </c>
     </row>
@@ -8216,17 +8216,17 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>(2, 1, 0)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -8235,22 +8235,22 @@
         </is>
       </c>
       <c r="F170" t="n">
-        <v>1144.81</v>
+        <v>1005.06</v>
       </c>
       <c r="G170" t="n">
-        <v>938.73</v>
+        <v>968.0599999999999</v>
       </c>
       <c r="H170" t="n">
-        <v>18.81</v>
+        <v>15.08</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>[3216.17, 8157.66, 4716.25]</t>
+          <t>[6110.81, 8771.68, 7119.48]</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>[3080.6, 6417.0, 3776.3]</t>
+          <t>[5524.8, 7606.3, 5966.7]</t>
         </is>
       </c>
     </row>
@@ -8262,12 +8262,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -8277,26 +8277,26 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>2531.73</v>
+        <v>1360.84</v>
       </c>
       <c r="G171" t="n">
-        <v>1759.13</v>
+        <v>1220.35</v>
       </c>
       <c r="H171" t="n">
-        <v>29.22</v>
+        <v>14.83</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>[10750.2, 4305.87, 7194.52]</t>
+          <t>[8376.98, 6785.54, 12114.02]</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>[6417.0, 3776.3, 6779.9]</t>
+          <t>[7606.3, 5966.7, 10042.5]</t>
         </is>
       </c>
     </row>
@@ -8308,41 +8308,41 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>(0, 1, 0)</t>
+          <t>(2, 1, 2)</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(2, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>4256.86</v>
+        <v>1803.56</v>
       </c>
       <c r="G172" t="n">
-        <v>4218.29</v>
+        <v>1625.54</v>
       </c>
       <c r="H172" t="n">
-        <v>29.16</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>[8537.08, 9819.69, 13194.86]</t>
+          <t>[24115.61, 18875.27, 16147.39]</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>[13562.1, 13681.1, 16963.3]</t>
+          <t>[24757.9, 20555.9, 18701.1]</t>
         </is>
       </c>
     </row>
@@ -8354,41 +8354,41 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>(2, 1, 2)</t>
+          <t>(0, 1, 0)</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>(0, 1, 2, 12)</t>
+          <t>(2, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>5112.37</v>
+        <v>2116.72</v>
       </c>
       <c r="G173" t="n">
-        <v>4807.02</v>
+        <v>1975.91</v>
       </c>
       <c r="H173" t="n">
-        <v>27.7</v>
+        <v>11.23</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>[16138.24, 22311.22, 26302.39]</t>
+          <t>[19497.64, 16748.89, 13202.74]</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>[13681.1, 16963.3, 19686.4]</t>
+          <t>[20555.9, 18701.1, 16120.0]</t>
         </is>
       </c>
     </row>
@@ -8400,17 +8400,17 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>(2, 1, 2)</t>
+          <t>(0, 1, 0)</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -8419,22 +8419,22 @@
         </is>
       </c>
       <c r="F174" t="n">
-        <v>3630.36</v>
+        <v>2263.68</v>
       </c>
       <c r="G174" t="n">
-        <v>3151.54</v>
+        <v>2103.02</v>
       </c>
       <c r="H174" t="n">
-        <v>15.25</v>
+        <v>12.33</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>[18695.55, 21714.52, 28261.76]</t>
+          <t>[17664.42, 13930.5, 14177.31]</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>[16963.3, 19686.4, 22567.5]</t>
+          <t>[18701.1, 16120.0, 17260.2]</t>
         </is>
       </c>
     </row>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -8465,22 +8465,22 @@
         </is>
       </c>
       <c r="F175" t="n">
-        <v>2975.4</v>
+        <v>4185.31</v>
       </c>
       <c r="G175" t="n">
-        <v>2367.16</v>
+        <v>3455.16</v>
       </c>
       <c r="H175" t="n">
-        <v>9.52</v>
+        <v>21.82</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>[19567.71, 25018.43, 31061.37]</t>
+          <t>[14753.64, 15018.04, 8604.56]</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>[19686.4, 22567.5, 26529.5]</t>
+          <t>[16120.0, 17260.2, 15361.5]</t>
         </is>
       </c>
     </row>
@@ -8492,41 +8492,41 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>(0, 1, 0)</t>
+          <t>(2, 1, 2)</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>(2, 1, 0, 12)</t>
+          <t>(1, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>3797.96</v>
+        <v>3823.61</v>
       </c>
       <c r="G176" t="n">
-        <v>3697.51</v>
+        <v>3224.22</v>
       </c>
       <c r="H176" t="n">
-        <v>14.52</v>
+        <v>20.7</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>[25172.58, 31257.31, 30259.52]</t>
+          <t>[16870.84, 10163.77, 11615.71]</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>[22567.5, 26529.5, 26499.9]</t>
+          <t>[17260.2, 15361.5, 15701.3]</t>
         </is>
       </c>
     </row>
@@ -8538,17 +8538,17 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>(0, 1, 0)</t>
+          <t>(2, 1, 3)</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -8557,22 +8557,22 @@
         </is>
       </c>
       <c r="F177" t="n">
-        <v>911.0599999999999</v>
+        <v>4693.8</v>
       </c>
       <c r="G177" t="n">
-        <v>697.63</v>
+        <v>4666.54</v>
       </c>
       <c r="H177" t="n">
-        <v>2.63</v>
+        <v>28.38</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>[27987.89, 27101.66, 24790.64]</t>
+          <t>[9983.58, 11334.2, 14804.41]</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>[26529.5, 26499.9, 24757.9]</t>
+          <t>[15361.5, 15701.3, 19059.0]</t>
         </is>
       </c>
     </row>
@@ -8584,41 +8584,41 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>(2, 1, 3)</t>
+          <t>(2, 0, 2)</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>(0, 1, 2, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F178" t="n">
-        <v>1423.9</v>
+        <v>5665.54</v>
       </c>
       <c r="G178" t="n">
-        <v>1358.53</v>
+        <v>5075.71</v>
       </c>
       <c r="H178" t="n">
-        <v>5.94</v>
+        <v>25.68</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>[25574.42, 23546.38, 18617.3]</t>
+          <t>[17446.88, 24710.76, 29425.09]</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>[26499.9, 24757.9, 20555.9]</t>
+          <t>[15701.3, 19059.0, 21595.3]</t>
         </is>
       </c>
     </row>
@@ -8630,41 +8630,41 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>(2, 1, 2)</t>
+          <t>(3, 0, 3)</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>(2, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F179" t="n">
-        <v>1803.56</v>
+        <v>4245.62</v>
       </c>
       <c r="G179" t="n">
-        <v>1625.54</v>
+        <v>3915.31</v>
       </c>
       <c r="H179" t="n">
-        <v>8.140000000000001</v>
+        <v>17.77</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>[24115.61, 18875.27, 16147.39]</t>
+          <t>[21731.23, 24433.75, 30093.45]</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>[24757.9, 20555.9, 18701.1]</t>
+          <t>[19059.0, 21595.3, 23858.2]</t>
         </is>
       </c>
     </row>
@@ -8676,41 +8676,41 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>(0, 1, 0)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>(2, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F180" t="n">
-        <v>2116.72</v>
+        <v>2459.04</v>
       </c>
       <c r="G180" t="n">
-        <v>1975.91</v>
+        <v>2158.34</v>
       </c>
       <c r="H180" t="n">
-        <v>11.23</v>
+        <v>8.35</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>[19497.64, 16748.89, 13202.74]</t>
+          <t>[22091.96, 26955.9, 32352.37]</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>[20555.9, 18701.1, 16120.0]</t>
+          <t>[21595.3, 23858.2, 29471.7]</t>
         </is>
       </c>
     </row>
@@ -8722,41 +8722,41 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>(0, 1, 0)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>(2, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>2263.68</v>
+        <v>2573.23</v>
       </c>
       <c r="G181" t="n">
-        <v>2103.02</v>
+        <v>2560.22</v>
       </c>
       <c r="H181" t="n">
-        <v>12.33</v>
+        <v>9.49</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>[17664.42, 13930.5, 14177.31]</t>
+          <t>[26394.71, 31727.88, 31261.17]</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>[18701.1, 16120.0, 17260.2]</t>
+          <t>[23858.2, 29471.7, 28373.2]</t>
         </is>
       </c>
     </row>
@@ -8768,41 +8768,41 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>(0, 1, 3)</t>
+          <t>(0, 1, 0)</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(2, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>8211.889999999999</v>
+        <v>1668.27</v>
       </c>
       <c r="G182" t="n">
-        <v>8200.5</v>
+        <v>1476.54</v>
       </c>
       <c r="H182" t="n">
-        <v>43.99</v>
+        <v>4.68</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>[8745.86, 10213.64, 12710.81]</t>
+          <t>[41727.14, 37292.01, 23833.33]</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>[16696.6, 18055.5, 21519.7]</t>
+          <t>[43225.3, 37806.9, 26249.9]</t>
         </is>
       </c>
     </row>
@@ -8814,17 +8814,17 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>(0, 1, 3)</t>
+          <t>(0, 1, 0)</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -8833,22 +8833,22 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>12852.56</v>
+        <v>2494.84</v>
       </c>
       <c r="G183" t="n">
-        <v>9063.5</v>
+        <v>2108.9</v>
       </c>
       <c r="H183" t="n">
-        <v>30.42</v>
+        <v>9.15</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>[19580.62, 25300.22, 55430.05]</t>
+          <t>[38629.78, 24691.63, 16471.35]</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>[18055.5, 21519.7, 33545.2]</t>
+          <t>[37806.9, 26249.9, 20416.9]</t>
         </is>
       </c>
     </row>
@@ -8860,17 +8860,17 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>(2, 1, 2)</t>
+          <t>(0, 1, 0)</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -8879,22 +8879,22 @@
         </is>
       </c>
       <c r="F184" t="n">
-        <v>15201.99</v>
+        <v>4205.45</v>
       </c>
       <c r="G184" t="n">
-        <v>12977.47</v>
+        <v>3960.6</v>
       </c>
       <c r="H184" t="n">
-        <v>37.11</v>
+        <v>17.5</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>[23462.25, 50396.39, 58818.07]</t>
+          <t>[24164.74, 16119.47, 17908.27]</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>[21519.7, 33545.2, 38679.4]</t>
+          <t>[26249.9, 20416.9, 23407.5]</t>
         </is>
       </c>
     </row>
@@ -8906,17 +8906,17 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>(2, 1, 2)</t>
+          <t>(0, 1, 0)</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -8925,22 +8925,22 @@
         </is>
       </c>
       <c r="F185" t="n">
-        <v>16048.57</v>
+        <v>5041.1</v>
       </c>
       <c r="G185" t="n">
-        <v>15753.17</v>
+        <v>4684.99</v>
       </c>
       <c r="H185" t="n">
-        <v>39.92</v>
+        <v>23.83</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>[47757.69, 51694.2, 65821.43]</t>
+          <t>[17534.24, 19482.36, 10597.33]</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>[33545.2, 38679.4, 45789.2]</t>
+          <t>[20416.9, 23407.5, 17844.5]</t>
         </is>
       </c>
     </row>
@@ -8952,41 +8952,41 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>(0, 1, 0)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>(2, 1, 0, 12)</t>
+          <t>(2, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F186" t="n">
-        <v>2012.89</v>
+        <v>3447.83</v>
       </c>
       <c r="G186" t="n">
-        <v>1716.77</v>
+        <v>2929.48</v>
       </c>
       <c r="H186" t="n">
-        <v>3.83</v>
+        <v>15.88</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>[38317.91, 47655.36, 48113.87]</t>
+          <t>[23019.38, 13305.75, 14920.02]</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>[38679.4, 45789.2, 45191.2]</t>
+          <t>[23407.5, 17844.5, 18781.6]</t>
         </is>
       </c>
     </row>
@@ -8998,41 +8998,41 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>(2, 1, 2)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>(2, 1, 0, 12)</t>
+          <t>(2, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F187" t="n">
-        <v>2637.03</v>
+        <v>4005.04</v>
       </c>
       <c r="G187" t="n">
-        <v>1904.47</v>
+        <v>3995.11</v>
       </c>
       <c r="H187" t="n">
-        <v>4.36</v>
+        <v>20.39</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>[45788.58, 43842.1, 38861.62]</t>
+          <t>[13501.41, 15128.82, 18963.34]</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>[45789.2, 45191.2, 43225.3]</t>
+          <t>[17844.5, 18781.6, 22952.8]</t>
         </is>
       </c>
     </row>
@@ -9044,41 +9044,41 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>(0, 1, 0)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>(2, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F188" t="n">
-        <v>703.21</v>
+        <v>3872.63</v>
       </c>
       <c r="G188" t="n">
-        <v>639.41</v>
+        <v>2849.43</v>
       </c>
       <c r="H188" t="n">
-        <v>1.48</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>[46228.23, 42685.17, 38147.98]</t>
+          <t>[19661.01, 24065.81, 40896.18]</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>[45191.2, 43225.3, 37806.9]</t>
+          <t>[18781.6, 22952.8, 34340.3]</t>
         </is>
       </c>
     </row>
@@ -9090,41 +9090,41 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>(0, 1, 0)</t>
+          <t>(1, 0, 3)</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>(2, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F189" t="n">
-        <v>1668.27</v>
+        <v>5402.58</v>
       </c>
       <c r="G189" t="n">
-        <v>1476.54</v>
+        <v>4589.58</v>
       </c>
       <c r="H189" t="n">
-        <v>4.68</v>
+        <v>12.88</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>[41727.14, 37292.01, 23833.33]</t>
+          <t>[23557.84, 40394.88, 45823.93]</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>[43225.3, 37806.9, 26249.9]</t>
+          <t>[22952.8, 34340.3, 38714.8]</t>
         </is>
       </c>
     </row>
@@ -9136,41 +9136,41 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>(0, 1, 0)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>(2, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F190" t="n">
-        <v>2494.84</v>
+        <v>6874.79</v>
       </c>
       <c r="G190" t="n">
-        <v>2108.9</v>
+        <v>6655.84</v>
       </c>
       <c r="H190" t="n">
-        <v>9.15</v>
+        <v>16.61</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>[38629.78, 24691.63, 16471.35]</t>
+          <t>[39094.66, 45005.24, 54124.21]</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>[37806.9, 26249.9, 20416.9]</t>
+          <t>[34340.3, 38714.8, 45201.5]</t>
         </is>
       </c>
     </row>
@@ -9182,41 +9182,41 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>(0, 1, 0)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>(2, 1, 0, 12)</t>
+          <t>(2, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F191" t="n">
-        <v>4205.45</v>
+        <v>2346.67</v>
       </c>
       <c r="G191" t="n">
-        <v>3960.6</v>
+        <v>2204.64</v>
       </c>
       <c r="H191" t="n">
-        <v>17.5</v>
+        <v>4.98</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>[24164.74, 16119.47, 17908.27]</t>
+          <t>[39930.01, 48386.06, 48894.85]</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>[26249.9, 20416.9, 23407.5]</t>
+          <t>[38714.8, 45201.5, 46680.7]</t>
         </is>
       </c>
     </row>
@@ -9228,41 +9228,41 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>(0, 1, 0)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F192" t="n">
-        <v>15397.29</v>
+        <v>2453.4</v>
       </c>
       <c r="G192" t="n">
-        <v>15270.78</v>
+        <v>2394.94</v>
       </c>
       <c r="H192" t="n">
-        <v>49.79</v>
+        <v>6.81</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>[13151.56, 14482.02, 18722.56]</t>
+          <t>[36862.23, 33622.72, 29858.44]</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>[26380.9, 29132.2, 36655.4]</t>
+          <t>[38641.4, 35950.3, 32936.5]</t>
         </is>
       </c>
     </row>
@@ -9274,17 +9274,17 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>(0, 1, 0)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -9293,22 +9293,22 @@
         </is>
       </c>
       <c r="F193" t="n">
-        <v>1507.45</v>
+        <v>1206.05</v>
       </c>
       <c r="G193" t="n">
-        <v>1182.31</v>
+        <v>1142.41</v>
       </c>
       <c r="H193" t="n">
-        <v>2.94</v>
+        <v>3.5</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>[29105.81, 37859.19, 44910.76]</t>
+          <t>[35319.05, 31370.46, 29530.66]</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>[29132.2, 36655.4, 42594.0]</t>
+          <t>[35950.3, 32936.5, 30760.6]</t>
         </is>
       </c>
     </row>
@@ -9320,17 +9320,17 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>(0, 1, 0)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -9339,22 +9339,22 @@
         </is>
       </c>
       <c r="F194" t="n">
-        <v>2434.46</v>
+        <v>754.03</v>
       </c>
       <c r="G194" t="n">
-        <v>2289.6</v>
+        <v>717.27</v>
       </c>
       <c r="H194" t="n">
-        <v>5.11</v>
+        <v>2.3</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>[37896.58, 44958.26, 54212.86]</t>
+          <t>[31932.56, 30047.05, 29051.11]</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>[36655.4, 42594.0, 50949.5]</t>
+          <t>[32936.5, 30760.6, 28616.8]</t>
         </is>
       </c>
     </row>
@@ -9366,17 +9366,17 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>(0, 1, 0)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -9385,22 +9385,22 @@
         </is>
       </c>
       <c r="F195" t="n">
-        <v>1011.83</v>
+        <v>6048.71</v>
       </c>
       <c r="G195" t="n">
-        <v>871.04</v>
+        <v>3972.96</v>
       </c>
       <c r="H195" t="n">
-        <v>1.81</v>
+        <v>12.21</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>[43487.53, 52439.57, 54594.68]</t>
+          <t>[30973.0, 29931.59, 22766.32]</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>[42594.0, 50949.5, 54824.2]</t>
+          <t>[30760.6, 28616.8, 33158.0]</t>
         </is>
       </c>
     </row>
@@ -9412,17 +9412,17 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>(0, 1, 0)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -9431,22 +9431,22 @@
         </is>
       </c>
       <c r="F196" t="n">
-        <v>2479.11</v>
+        <v>8524.48</v>
       </c>
       <c r="G196" t="n">
-        <v>1940.8</v>
+        <v>7316.72</v>
       </c>
       <c r="H196" t="n">
-        <v>4.5</v>
+        <v>21.53</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>[51362.33, 53467.7, 43696.38]</t>
+          <t>[29748.61, 22656.02, 25307.33]</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>[50949.5, 54824.2, 39643.3]</t>
+          <t>[28616.8, 33158.0, 35623.7]</t>
         </is>
       </c>
     </row>
@@ -9458,17 +9458,17 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>(0, 1, 0)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -9477,22 +9477,22 @@
         </is>
       </c>
       <c r="F197" t="n">
-        <v>2445.68</v>
+        <v>11854.45</v>
       </c>
       <c r="G197" t="n">
-        <v>2106.31</v>
+        <v>11845.54</v>
       </c>
       <c r="H197" t="n">
-        <v>4.91</v>
+        <v>31.81</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>[53031.11, 43404.1, 39406.45]</t>
+          <t>[21594.85, 24143.74, 31592.88]</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>[54824.2, 39643.3, 38641.4]</t>
+          <t>[33158.0, 35623.7, 44086.4]</t>
         </is>
       </c>
     </row>
@@ -9504,41 +9504,41 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>(0, 1, 0)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>(0, 1, 2, 12)</t>
+          <t>(2, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F198" t="n">
-        <v>3281.39</v>
+        <v>5101.49</v>
       </c>
       <c r="G198" t="n">
-        <v>2529.5</v>
+        <v>4394.3</v>
       </c>
       <c r="H198" t="n">
-        <v>6.44</v>
+        <v>9.52</v>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>[44912.31, 40762.92, 35752.34]</t>
+          <t>[36950.4, 48277.99, 57655.1]</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>[39643.3, 38641.4, 35950.3]</t>
+          <t>[35623.7, 44086.4, 49990.5]</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -9565,26 +9565,26 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>(0, 1, 2, 12)</t>
+          <t>(2, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F199" t="n">
-        <v>2453.4</v>
+        <v>6101.62</v>
       </c>
       <c r="G199" t="n">
-        <v>2394.94</v>
+        <v>5590</v>
       </c>
       <c r="H199" t="n">
-        <v>6.81</v>
+        <v>10.52</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>[36862.23, 33622.72, 29858.44]</t>
+          <t>[46608.03, 55732.2, 67809.79]</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>[38641.4, 35950.3, 32936.5]</t>
+          <t>[44086.4, 49990.5, 59303.1]</t>
         </is>
       </c>
     </row>
@@ -9596,12 +9596,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -9611,26 +9611,26 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>(0, 1, 2, 12)</t>
+          <t>(2, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F200" t="n">
-        <v>1206.05</v>
+        <v>3169.95</v>
       </c>
       <c r="G200" t="n">
-        <v>1142.41</v>
+        <v>3101.22</v>
       </c>
       <c r="H200" t="n">
-        <v>3.5</v>
+        <v>5.38</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>[35319.05, 31370.46, 29530.66]</t>
+          <t>[52171.23, 62759.61, 65369.33]</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>[35950.3, 32936.5, 30760.6]</t>
+          <t>[49990.5, 59303.1, 61702.9]</t>
         </is>
       </c>
     </row>
@@ -9642,12 +9642,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -9657,26 +9657,26 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>(0, 1, 2, 12)</t>
+          <t>(2, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F201" t="n">
-        <v>754.03</v>
+        <v>6177.49</v>
       </c>
       <c r="G201" t="n">
-        <v>717.27</v>
+        <v>4916.65</v>
       </c>
       <c r="H201" t="n">
-        <v>2.3</v>
+        <v>10.3</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>[31932.56, 30047.05, 29051.11]</t>
+          <t>[60979.23, 64619.55, 53652.66]</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>[32936.5, 30760.6, 28616.8]</t>
+          <t>[59303.1, 61702.9, 43495.5]</t>
         </is>
       </c>
     </row>
